--- a/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>AATC</t>
   </si>
@@ -656,192 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E8" s="3">
         <v>6700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L8" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M8" s="3">
         <v>3800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="N8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="T8" s="3">
         <v>3700</v>
       </c>
-      <c r="G8" s="3">
-        <v>2700</v>
-      </c>
-      <c r="H8" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J8" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K8" s="3">
-        <v>3300</v>
-      </c>
-      <c r="L8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="M8" s="3">
-        <v>3000</v>
-      </c>
-      <c r="N8" s="3">
-        <v>2900</v>
-      </c>
-      <c r="O8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="P8" s="3">
-        <v>3400</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>3200</v>
-      </c>
-      <c r="R8" s="3">
-        <v>3400</v>
-      </c>
-      <c r="S8" s="3">
-        <v>3700</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
         <v>900</v>
-      </c>
-      <c r="E9" s="3">
-        <v>700</v>
       </c>
       <c r="F9" s="3">
         <v>900</v>
       </c>
       <c r="G9" s="3">
+        <v>900</v>
+      </c>
+      <c r="H9" s="3">
         <v>800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>800</v>
-      </c>
-      <c r="M9" s="3">
-        <v>700</v>
       </c>
       <c r="N9" s="3">
         <v>700</v>
       </c>
       <c r="O9" s="3">
+        <v>700</v>
+      </c>
+      <c r="P9" s="3">
         <v>900</v>
-      </c>
-      <c r="P9" s="3">
-        <v>600</v>
       </c>
       <c r="Q9" s="3">
         <v>600</v>
@@ -850,69 +857,75 @@
         <v>600</v>
       </c>
       <c r="S9" s="3">
+        <v>600</v>
+      </c>
+      <c r="T9" s="3">
         <v>500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E10" s="3">
         <v>5800</v>
       </c>
-      <c r="E10" s="3">
-        <v>3100</v>
-      </c>
       <c r="F10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G10" s="3">
         <v>2800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,16 +946,17 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>700</v>
+      </c>
+      <c r="E12" s="3">
         <v>1300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>600</v>
       </c>
       <c r="F12" s="3">
         <v>600</v>
@@ -951,25 +965,25 @@
         <v>600</v>
       </c>
       <c r="H12" s="3">
+        <v>600</v>
+      </c>
+      <c r="I12" s="3">
         <v>1000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>600</v>
-      </c>
-      <c r="L12" s="3">
-        <v>500</v>
       </c>
       <c r="M12" s="3">
         <v>500</v>
       </c>
       <c r="N12" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="O12" s="3">
         <v>800</v>
@@ -978,19 +992,22 @@
         <v>800</v>
       </c>
       <c r="Q12" s="3">
+        <v>800</v>
+      </c>
+      <c r="R12" s="3">
         <v>900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>800</v>
-      </c>
-      <c r="S12" s="3">
-        <v>700</v>
       </c>
       <c r="T12" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1045,8 +1062,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1068,21 +1088,21 @@
       <c r="I14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" s="3">
         <v>-900</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1101,8 +1121,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I17" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="N17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="S17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="T17" s="3">
         <v>2800</v>
       </c>
-      <c r="F17" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J17" s="3">
-        <v>3000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2600</v>
-      </c>
-      <c r="L17" s="3">
-        <v>2900</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="N17" s="3">
-        <v>3000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>3100</v>
-      </c>
-      <c r="P17" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>3400</v>
-      </c>
-      <c r="R17" s="3">
-        <v>3500</v>
-      </c>
-      <c r="S17" s="3">
-        <v>2800</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E18" s="3">
         <v>2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1310,17 +1343,18 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
-        <v>100</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
@@ -1366,64 +1400,70 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E21" s="3">
         <v>2900</v>
       </c>
-      <c r="E21" s="3">
-        <v>1300</v>
-      </c>
       <c r="F21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G21" s="3">
         <v>900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1448,8 +1488,8 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>17</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>17</v>
@@ -1457,11 +1497,11 @@
       <c r="M22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3" t="s">
+      <c r="N22" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>17</v>
@@ -1478,120 +1518,129 @@
       <c r="T22" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E23" s="3">
         <v>2400</v>
       </c>
-      <c r="E23" s="3">
-        <v>1100</v>
-      </c>
       <c r="F23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G23" s="3">
         <v>700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>200</v>
       </c>
       <c r="F24" s="3">
         <v>200</v>
       </c>
       <c r="G24" s="3">
+        <v>200</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
-      </c>
-      <c r="L24" s="3">
-        <v>200</v>
       </c>
       <c r="M24" s="3">
         <v>200</v>
       </c>
       <c r="N24" s="3">
+        <v>200</v>
+      </c>
+      <c r="O24" s="3">
         <v>-500</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-5200</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E26" s="3">
         <v>1900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>200</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-100</v>
       </c>
       <c r="R26" s="3">
         <v>-100</v>
       </c>
       <c r="S26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T26" s="3">
         <v>6100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-600</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>200</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-100</v>
       </c>
       <c r="R27" s="3">
         <v>-100</v>
       </c>
       <c r="S27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T27" s="3">
         <v>6100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,34 +1872,37 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E29" s="3">
         <v>100</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3">
+        <v>100</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>700</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,17 +2049,20 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
-        <v>-100</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
@@ -2038,64 +2108,70 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E33" s="3">
         <v>2000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>100</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>200</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-100</v>
       </c>
       <c r="R33" s="3">
         <v>-100</v>
       </c>
       <c r="S33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T33" s="3">
         <v>6100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E35" s="3">
         <v>2000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>100</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>200</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-100</v>
       </c>
       <c r="R35" s="3">
         <v>-100</v>
       </c>
       <c r="S35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T35" s="3">
         <v>6100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,87 +2397,91 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E41" s="3">
         <v>2900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E42" s="3">
         <v>3200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>400</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>17</v>
@@ -2408,8 +2498,8 @@
       <c r="O42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2423,120 +2513,129 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E43" s="3">
         <v>4100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4400</v>
-      </c>
-      <c r="F43" s="3">
-        <v>3700</v>
       </c>
       <c r="G43" s="3">
         <v>3700</v>
       </c>
       <c r="H43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I43" s="3">
         <v>2800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E44" s="3">
         <v>2500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1500</v>
-      </c>
-      <c r="I44" s="3">
-        <v>1400</v>
       </c>
       <c r="J44" s="3">
         <v>1400</v>
       </c>
       <c r="K44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L44" s="3">
         <v>1500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>700</v>
-      </c>
-      <c r="M44" s="3">
-        <v>800</v>
       </c>
       <c r="N44" s="3">
         <v>800</v>
       </c>
       <c r="O44" s="3">
+        <v>800</v>
+      </c>
+      <c r="P44" s="3">
         <v>400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>700</v>
-      </c>
-      <c r="R44" s="3">
-        <v>800</v>
       </c>
       <c r="S44" s="3">
         <v>800</v>
       </c>
       <c r="T44" s="3">
+        <v>800</v>
+      </c>
+      <c r="U44" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2544,34 +2643,34 @@
         <v>400</v>
       </c>
       <c r="E45" s="3">
+        <v>400</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>400</v>
       </c>
       <c r="M45" s="3">
         <v>400</v>
       </c>
       <c r="N45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O45" s="3">
         <v>500</v>
@@ -2580,10 +2679,10 @@
         <v>500</v>
       </c>
       <c r="Q45" s="3">
+        <v>500</v>
+      </c>
+      <c r="R45" s="3">
         <v>600</v>
-      </c>
-      <c r="R45" s="3">
-        <v>500</v>
       </c>
       <c r="S45" s="3">
         <v>500</v>
@@ -2591,87 +2690,93 @@
       <c r="T45" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E46" s="3">
         <v>13100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12400</v>
-      </c>
-      <c r="K46" s="3">
-        <v>13100</v>
       </c>
       <c r="L46" s="3">
         <v>13100</v>
       </c>
       <c r="M46" s="3">
+        <v>13100</v>
+      </c>
+      <c r="N46" s="3">
         <v>12300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>100</v>
+      </c>
+      <c r="E47" s="3">
         <v>400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2300</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>17</v>
@@ -2688,8 +2793,8 @@
       <c r="O47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2703,13 +2808,16 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="E48" s="3">
         <v>2100</v>
@@ -2718,7 +2826,7 @@
         <v>2100</v>
       </c>
       <c r="G48" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="H48" s="3">
         <v>2200</v>
@@ -2727,25 +2835,25 @@
         <v>2200</v>
       </c>
       <c r="J48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K48" s="3">
         <v>2300</v>
-      </c>
-      <c r="K48" s="3">
-        <v>300</v>
       </c>
       <c r="L48" s="3">
         <v>300</v>
       </c>
       <c r="M48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N48" s="3">
         <v>400</v>
       </c>
       <c r="O48" s="3">
+        <v>400</v>
+      </c>
+      <c r="P48" s="3">
         <v>500</v>
-      </c>
-      <c r="P48" s="3">
-        <v>600</v>
       </c>
       <c r="Q48" s="3">
         <v>600</v>
@@ -2754,69 +2862,75 @@
         <v>600</v>
       </c>
       <c r="S48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="T48" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E49" s="3">
         <v>2200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2800</v>
-      </c>
-      <c r="H49" s="3">
-        <v>3000</v>
       </c>
       <c r="I49" s="3">
         <v>3000</v>
       </c>
       <c r="J49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K49" s="3">
         <v>2900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3700</v>
-      </c>
-      <c r="R49" s="3">
-        <v>3900</v>
       </c>
       <c r="S49" s="3">
         <v>3900</v>
       </c>
       <c r="T49" s="3">
+        <v>3900</v>
+      </c>
+      <c r="U49" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,25 +3044,28 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E52" s="3">
         <v>4000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>4800</v>
       </c>
       <c r="I52" s="3">
         <v>4800</v>
@@ -2954,19 +3074,19 @@
         <v>4800</v>
       </c>
       <c r="K52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="L52" s="3">
         <v>5200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5700</v>
-      </c>
-      <c r="O52" s="3">
-        <v>5200</v>
       </c>
       <c r="P52" s="3">
         <v>5200</v>
@@ -2978,13 +3098,16 @@
         <v>5200</v>
       </c>
       <c r="S52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="T52" s="3">
         <v>5300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E54" s="3">
         <v>21800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>22000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>20700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>20000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19100</v>
-      </c>
-      <c r="R54" s="3">
-        <v>19200</v>
       </c>
       <c r="S54" s="3">
         <v>19200</v>
       </c>
       <c r="T54" s="3">
+        <v>19200</v>
+      </c>
+      <c r="U54" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,13 +3269,14 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
         <v>400</v>
@@ -3154,40 +3285,40 @@
         <v>400</v>
       </c>
       <c r="G57" s="3">
+        <v>400</v>
+      </c>
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
       </c>
       <c r="L57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M57" s="3">
         <v>300</v>
       </c>
       <c r="N57" s="3">
+        <v>300</v>
+      </c>
+      <c r="O57" s="3">
         <v>500</v>
-      </c>
-      <c r="O57" s="3">
-        <v>300</v>
       </c>
       <c r="P57" s="3">
         <v>300</v>
       </c>
       <c r="Q57" s="3">
+        <v>300</v>
+      </c>
+      <c r="R57" s="3">
         <v>600</v>
-      </c>
-      <c r="R57" s="3">
-        <v>400</v>
       </c>
       <c r="S57" s="3">
         <v>400</v>
@@ -3195,8 +3326,11 @@
       <c r="T57" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3222,7 +3356,7 @@
         <v>100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3231,16 +3365,16 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>400</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>17</v>
@@ -3251,19 +3385,22 @@
       <c r="T58" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>500</v>
+        <v>1100</v>
       </c>
       <c r="E59" s="3">
         <v>500</v>
       </c>
       <c r="F59" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G59" s="3">
         <v>400</v>
@@ -3272,99 +3409,105 @@
         <v>400</v>
       </c>
       <c r="I59" s="3">
+        <v>400</v>
+      </c>
+      <c r="J59" s="3">
         <v>500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>600</v>
       </c>
       <c r="K59" s="3">
         <v>600</v>
       </c>
       <c r="L59" s="3">
+        <v>600</v>
+      </c>
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="E60" s="3">
         <v>1000</v>
       </c>
       <c r="F60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G60" s="3">
         <v>900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1500</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1000</v>
       </c>
       <c r="I60" s="3">
         <v>1000</v>
       </c>
       <c r="J60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K60" s="3">
         <v>900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
-      </c>
-      <c r="N60" s="3">
-        <v>1500</v>
       </c>
       <c r="O60" s="3">
         <v>1500</v>
       </c>
       <c r="P60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q60" s="3">
         <v>1400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3384,13 +3527,13 @@
         <v>1600</v>
       </c>
       <c r="I61" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="J61" s="3">
         <v>1700</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -3399,17 +3542,17 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>500</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3419,28 +3562,31 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>17</v>
+      <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
@@ -3473,10 +3619,13 @@
         <v>0</v>
       </c>
       <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="E66" s="3">
         <v>2600</v>
       </c>
       <c r="F66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G66" s="3">
         <v>2500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2000</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>1300</v>
       </c>
       <c r="R66" s="3">
         <v>1300</v>
       </c>
       <c r="S66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T66" s="3">
         <v>1400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,8 +4116,11 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3959,50 +4133,53 @@
       <c r="F72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G72" s="3">
-        <v>-6300</v>
+      <c r="G72" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H72" s="3">
         <v>-6300</v>
       </c>
       <c r="I72" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="J72" s="3">
         <v>-5800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5100</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-4300</v>
       </c>
       <c r="L72" s="3">
         <v>-4300</v>
       </c>
       <c r="M72" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="N72" s="3">
         <v>-4400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E76" s="3">
         <v>19200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E81" s="3">
         <v>2000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>100</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>200</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-100</v>
       </c>
       <c r="R81" s="3">
         <v>-100</v>
       </c>
       <c r="S81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T81" s="3">
         <v>6100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,16 +4618,17 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>500</v>
-      </c>
-      <c r="E83" s="3">
-        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -4438,10 +4637,10 @@
         <v>200</v>
       </c>
       <c r="H83" s="3">
+        <v>200</v>
+      </c>
+      <c r="I83" s="3">
         <v>500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>200</v>
       </c>
       <c r="J83" s="3">
         <v>200</v>
@@ -4462,10 +4661,10 @@
         <v>200</v>
       </c>
       <c r="P83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
@@ -4476,8 +4675,11 @@
       <c r="T83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E89" s="3">
         <v>2600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>100</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>600</v>
-      </c>
-      <c r="P89" s="3">
-        <v>500</v>
       </c>
       <c r="Q89" s="3">
         <v>500</v>
       </c>
       <c r="R89" s="3">
+        <v>500</v>
+      </c>
+      <c r="S89" s="3">
         <v>400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,8 +5054,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4843,32 +5064,32 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2400</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -4879,19 +5100,22 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,43 +5229,46 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E94" s="3">
         <v>600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2400</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M94" s="3">
         <v>-100</v>
       </c>
       <c r="N94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -5047,19 +5277,22 @@
         <v>0</v>
       </c>
       <c r="Q94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="T94" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,28 +5313,29 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>-1400</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>-600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-1300</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-600</v>
       </c>
       <c r="J96" s="3">
         <v>-600</v>
@@ -5110,7 +5344,7 @@
         <v>-600</v>
       </c>
       <c r="L96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,40 +5547,43 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1400</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
         <v>-700</v>
       </c>
       <c r="H100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1100</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-600</v>
       </c>
       <c r="L100" s="3">
         <v>-600</v>
       </c>
       <c r="M100" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -5346,11 +5592,11 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>900</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
@@ -5360,116 +5606,125 @@
       <c r="T100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
-      </c>
-      <c r="N101" s="3">
-        <v>100</v>
       </c>
       <c r="O101" s="3">
         <v>100</v>
       </c>
       <c r="P101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>400</v>
+      </c>
+      <c r="E102" s="3">
         <v>1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>AATC</t>
   </si>
@@ -656,166 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E8" s="3">
         <v>3800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M8" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="O8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="R8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="S8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="T8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="U8" s="3">
         <v>3700</v>
       </c>
-      <c r="H8" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I8" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K8" s="3">
-        <v>3200</v>
-      </c>
-      <c r="L8" s="3">
-        <v>3300</v>
-      </c>
-      <c r="M8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="N8" s="3">
-        <v>3000</v>
-      </c>
-      <c r="O8" s="3">
-        <v>2900</v>
-      </c>
-      <c r="P8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>3400</v>
-      </c>
-      <c r="R8" s="3">
-        <v>3200</v>
-      </c>
-      <c r="S8" s="3">
-        <v>3400</v>
-      </c>
-      <c r="T8" s="3">
-        <v>3700</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>200</v>
+      </c>
+      <c r="E9" s="3">
         <v>100</v>
-      </c>
-      <c r="E9" s="3">
-        <v>900</v>
       </c>
       <c r="F9" s="3">
         <v>900</v>
@@ -824,34 +830,34 @@
         <v>900</v>
       </c>
       <c r="H9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I9" s="3">
         <v>800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>800</v>
-      </c>
-      <c r="N9" s="3">
-        <v>700</v>
       </c>
       <c r="O9" s="3">
         <v>700</v>
       </c>
       <c r="P9" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q9" s="3">
         <v>900</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>600</v>
       </c>
       <c r="R9" s="3">
         <v>600</v>
@@ -860,72 +866,78 @@
         <v>600</v>
       </c>
       <c r="T9" s="3">
+        <v>600</v>
+      </c>
+      <c r="U9" s="3">
         <v>500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E10" s="3">
         <v>3700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="N10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="R10" s="3">
         <v>2800</v>
       </c>
-      <c r="H10" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J10" s="3">
-        <v>2200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="L10" s="3">
-        <v>2700</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="S10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="T10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="U10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="V10" s="3">
         <v>3000</v>
       </c>
-      <c r="N10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="O10" s="3">
-        <v>2200</v>
-      </c>
-      <c r="P10" s="3">
-        <v>2900</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="R10" s="3">
-        <v>2600</v>
-      </c>
-      <c r="S10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="T10" s="3">
-        <v>3200</v>
-      </c>
-      <c r="U10" s="3">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,19 +959,20 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>600</v>
+      </c>
+      <c r="E12" s="3">
         <v>700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1300</v>
-      </c>
-      <c r="F12" s="3">
-        <v>600</v>
       </c>
       <c r="G12" s="3">
         <v>600</v>
@@ -968,25 +981,25 @@
         <v>600</v>
       </c>
       <c r="I12" s="3">
+        <v>600</v>
+      </c>
+      <c r="J12" s="3">
         <v>1000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>600</v>
-      </c>
-      <c r="M12" s="3">
-        <v>500</v>
       </c>
       <c r="N12" s="3">
         <v>500</v>
       </c>
       <c r="O12" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="P12" s="3">
         <v>800</v>
@@ -995,19 +1008,22 @@
         <v>800</v>
       </c>
       <c r="R12" s="3">
+        <v>800</v>
+      </c>
+      <c r="S12" s="3">
         <v>900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>800</v>
-      </c>
-      <c r="T12" s="3">
-        <v>700</v>
       </c>
       <c r="U12" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1065,8 +1081,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1091,21 +1110,21 @@
       <c r="J14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O14" s="3">
         <v>-900</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1124,8 +1143,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1183,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L17" s="3">
         <v>3000</v>
       </c>
-      <c r="H17" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I17" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2700</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="O17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P17" s="3">
         <v>3000</v>
       </c>
-      <c r="L17" s="3">
-        <v>2600</v>
-      </c>
-      <c r="M17" s="3">
-        <v>2900</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="R17" s="3">
         <v>3000</v>
       </c>
-      <c r="P17" s="3">
-        <v>3100</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>3000</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>500</v>
+      </c>
+      <c r="E18" s="3">
         <v>1800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K18" s="3">
+        <v>100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>200</v>
+      </c>
+      <c r="M18" s="3">
         <v>700</v>
       </c>
-      <c r="H18" s="3">
-        <v>800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="J18" s="3">
-        <v>100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>200</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
+        <v>900</v>
+      </c>
+      <c r="O18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q18" s="3">
         <v>700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="R18" s="3">
+        <v>400</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U18" s="3">
         <v>900</v>
       </c>
-      <c r="N18" s="3">
-        <v>1400</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P18" s="3">
-        <v>700</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>400</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T18" s="3">
-        <v>900</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1344,25 +1376,26 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1403,67 +1436,73 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>900</v>
+      </c>
+      <c r="E21" s="3">
         <v>1900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K21" s="3">
+        <v>300</v>
+      </c>
+      <c r="L21" s="3">
+        <v>500</v>
+      </c>
+      <c r="M21" s="3">
         <v>900</v>
       </c>
-      <c r="H21" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>300</v>
-      </c>
-      <c r="K21" s="3">
-        <v>500</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="3">
         <v>900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="R21" s="3">
+        <v>600</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T21" s="3">
+        <v>100</v>
+      </c>
+      <c r="U21" s="3">
         <v>1100</v>
       </c>
-      <c r="N21" s="3">
-        <v>1600</v>
-      </c>
-      <c r="O21" s="3">
-        <v>100</v>
-      </c>
-      <c r="P21" s="3">
-        <v>900</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>600</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S21" s="3">
-        <v>100</v>
-      </c>
-      <c r="T21" s="3">
-        <v>1100</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1491,8 +1530,8 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>17</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>17</v>
@@ -1500,11 +1539,11 @@
       <c r="N22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3" t="s">
+      <c r="O22" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>17</v>
@@ -1521,126 +1560,135 @@
       <c r="U22" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>700</v>
+      </c>
+      <c r="E23" s="3">
         <v>1900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>300</v>
+      </c>
+      <c r="I23" s="3">
+        <v>800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <v>300</v>
+      </c>
+      <c r="M23" s="3">
         <v>700</v>
       </c>
-      <c r="H23" s="3">
-        <v>800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
-        <v>300</v>
-      </c>
-      <c r="L23" s="3">
-        <v>700</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>200</v>
       </c>
       <c r="G24" s="3">
         <v>200</v>
       </c>
       <c r="H24" s="3">
+        <v>200</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>200</v>
       </c>
       <c r="N24" s="3">
         <v>200</v>
       </c>
       <c r="O24" s="3">
+        <v>200</v>
+      </c>
+      <c r="P24" s="3">
         <v>-500</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-200</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-5200</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>800</v>
       </c>
-      <c r="G26" s="3">
-        <v>500</v>
-      </c>
       <c r="H26" s="3">
+        <v>100</v>
+      </c>
+      <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>200</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-100</v>
       </c>
       <c r="S26" s="3">
         <v>-100</v>
       </c>
       <c r="T26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U26" s="3">
         <v>6100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E27" s="3">
         <v>1500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>800</v>
       </c>
-      <c r="G27" s="3">
-        <v>500</v>
-      </c>
       <c r="H27" s="3">
+        <v>100</v>
+      </c>
+      <c r="I27" s="3">
         <v>600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>200</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-100</v>
       </c>
       <c r="S27" s="3">
         <v>-100</v>
       </c>
       <c r="T27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U27" s="3">
         <v>6100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,37 +1932,40 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>2100</v>
-      </c>
-      <c r="E29" s="3">
-        <v>100</v>
       </c>
       <c r="F29" s="3">
         <v>100</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>17</v>
+      <c r="G29" s="3">
+        <v>100</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>700</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -1934,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,25 +2118,28 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -2111,67 +2180,73 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E33" s="3">
         <v>3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>100</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>200</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-100</v>
       </c>
       <c r="S33" s="3">
         <v>-100</v>
       </c>
       <c r="T33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U33" s="3">
         <v>6100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E35" s="3">
         <v>3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>100</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>200</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-100</v>
       </c>
       <c r="S35" s="3">
         <v>-100</v>
       </c>
       <c r="T35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U35" s="3">
         <v>6100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,93 +2483,97 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E41" s="3">
         <v>3300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E42" s="3">
         <v>9200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>400</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>17</v>
@@ -2501,8 +2590,8 @@
       <c r="P42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2516,164 +2605,173 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E43" s="3">
         <v>4300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4400</v>
-      </c>
-      <c r="G43" s="3">
-        <v>3700</v>
       </c>
       <c r="H43" s="3">
         <v>3700</v>
       </c>
       <c r="I43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J43" s="3">
         <v>2800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1500</v>
-      </c>
-      <c r="J44" s="3">
-        <v>1400</v>
       </c>
       <c r="K44" s="3">
         <v>1400</v>
       </c>
       <c r="L44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M44" s="3">
         <v>1500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>700</v>
-      </c>
-      <c r="N44" s="3">
-        <v>800</v>
       </c>
       <c r="O44" s="3">
         <v>800</v>
       </c>
       <c r="P44" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q44" s="3">
         <v>400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>700</v>
-      </c>
-      <c r="S44" s="3">
-        <v>800</v>
       </c>
       <c r="T44" s="3">
         <v>800</v>
       </c>
       <c r="U44" s="3">
+        <v>800</v>
+      </c>
+      <c r="V44" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E45" s="3">
         <v>400</v>
       </c>
       <c r="F45" s="3">
+        <v>400</v>
+      </c>
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
-      </c>
-      <c r="M45" s="3">
-        <v>400</v>
       </c>
       <c r="N45" s="3">
         <v>400</v>
       </c>
       <c r="O45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P45" s="3">
         <v>500</v>
@@ -2682,10 +2780,10 @@
         <v>500</v>
       </c>
       <c r="R45" s="3">
+        <v>500</v>
+      </c>
+      <c r="S45" s="3">
         <v>600</v>
-      </c>
-      <c r="S45" s="3">
-        <v>500</v>
       </c>
       <c r="T45" s="3">
         <v>500</v>
@@ -2693,67 +2791,73 @@
       <c r="U45" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E46" s="3">
         <v>18900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12400</v>
-      </c>
-      <c r="L46" s="3">
-        <v>13100</v>
       </c>
       <c r="M46" s="3">
         <v>13100</v>
       </c>
       <c r="N46" s="3">
+        <v>13100</v>
+      </c>
+      <c r="O46" s="3">
         <v>12300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2761,25 +2865,25 @@
         <v>100</v>
       </c>
       <c r="E47" s="3">
+        <v>100</v>
+      </c>
+      <c r="F47" s="3">
         <v>400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2300</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>17</v>
@@ -2796,8 +2900,8 @@
       <c r="P47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2811,8 +2915,11 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2820,7 +2927,7 @@
         <v>2000</v>
       </c>
       <c r="E48" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="F48" s="3">
         <v>2100</v>
@@ -2829,7 +2936,7 @@
         <v>2100</v>
       </c>
       <c r="H48" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="I48" s="3">
         <v>2200</v>
@@ -2838,25 +2945,25 @@
         <v>2200</v>
       </c>
       <c r="K48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L48" s="3">
         <v>2300</v>
-      </c>
-      <c r="L48" s="3">
-        <v>300</v>
       </c>
       <c r="M48" s="3">
         <v>300</v>
       </c>
       <c r="N48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O48" s="3">
         <v>400</v>
       </c>
       <c r="P48" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q48" s="3">
         <v>500</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>600</v>
       </c>
       <c r="R48" s="3">
         <v>600</v>
@@ -2865,72 +2972,78 @@
         <v>600</v>
       </c>
       <c r="T48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="U48" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2800</v>
-      </c>
-      <c r="I49" s="3">
-        <v>3000</v>
       </c>
       <c r="J49" s="3">
         <v>3000</v>
       </c>
       <c r="K49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L49" s="3">
         <v>2900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3700</v>
-      </c>
-      <c r="S49" s="3">
-        <v>3900</v>
       </c>
       <c r="T49" s="3">
         <v>3900</v>
       </c>
       <c r="U49" s="3">
+        <v>3900</v>
+      </c>
+      <c r="V49" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,28 +3163,31 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E52" s="3">
         <v>2900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4700</v>
-      </c>
-      <c r="I52" s="3">
-        <v>4800</v>
       </c>
       <c r="J52" s="3">
         <v>4800</v>
@@ -3077,19 +3196,19 @@
         <v>4800</v>
       </c>
       <c r="L52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="M52" s="3">
         <v>5200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5700</v>
-      </c>
-      <c r="P52" s="3">
-        <v>5200</v>
       </c>
       <c r="Q52" s="3">
         <v>5200</v>
@@ -3101,13 +3220,16 @@
         <v>5200</v>
       </c>
       <c r="T52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="U52" s="3">
         <v>5300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E54" s="3">
         <v>25100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>20700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>20000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>19100</v>
-      </c>
-      <c r="S54" s="3">
-        <v>19200</v>
       </c>
       <c r="T54" s="3">
         <v>19200</v>
       </c>
       <c r="U54" s="3">
+        <v>19200</v>
+      </c>
+      <c r="V54" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,16 +3399,17 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>400</v>
       </c>
       <c r="F57" s="3">
         <v>400</v>
@@ -3288,40 +3418,40 @@
         <v>400</v>
       </c>
       <c r="H57" s="3">
+        <v>400</v>
+      </c>
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>200</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
       </c>
       <c r="M57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N57" s="3">
         <v>300</v>
       </c>
       <c r="O57" s="3">
+        <v>300</v>
+      </c>
+      <c r="P57" s="3">
         <v>500</v>
-      </c>
-      <c r="P57" s="3">
-        <v>300</v>
       </c>
       <c r="Q57" s="3">
         <v>300</v>
       </c>
       <c r="R57" s="3">
+        <v>300</v>
+      </c>
+      <c r="S57" s="3">
         <v>600</v>
-      </c>
-      <c r="S57" s="3">
-        <v>400</v>
       </c>
       <c r="T57" s="3">
         <v>400</v>
@@ -3329,8 +3459,11 @@
       <c r="U57" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3359,7 +3492,7 @@
         <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3368,16 +3501,16 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>400</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>17</v>
@@ -3388,22 +3521,25 @@
       <c r="U58" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1100</v>
-      </c>
-      <c r="E59" s="3">
-        <v>500</v>
       </c>
       <c r="F59" s="3">
         <v>500</v>
       </c>
       <c r="G59" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H59" s="3">
         <v>400</v>
@@ -3412,102 +3548,108 @@
         <v>400</v>
       </c>
       <c r="J59" s="3">
+        <v>400</v>
+      </c>
+      <c r="K59" s="3">
         <v>500</v>
-      </c>
-      <c r="K59" s="3">
-        <v>600</v>
       </c>
       <c r="L59" s="3">
         <v>600</v>
       </c>
       <c r="M59" s="3">
+        <v>600</v>
+      </c>
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1400</v>
-      </c>
-      <c r="E60" s="3">
-        <v>1000</v>
       </c>
       <c r="F60" s="3">
         <v>1000</v>
       </c>
       <c r="G60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H60" s="3">
         <v>900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1500</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1000</v>
       </c>
       <c r="J60" s="3">
         <v>1000</v>
       </c>
       <c r="K60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L60" s="3">
         <v>900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
-      </c>
-      <c r="O60" s="3">
-        <v>1500</v>
       </c>
       <c r="P60" s="3">
         <v>1500</v>
       </c>
       <c r="Q60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R60" s="3">
         <v>1400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3530,13 +3672,13 @@
         <v>1600</v>
       </c>
       <c r="J61" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="K61" s="3">
         <v>1700</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -3545,17 +3687,17 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>500</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3565,8 +3707,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3622,10 +3767,13 @@
         <v>0</v>
       </c>
       <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3000</v>
-      </c>
-      <c r="E66" s="3">
-        <v>2600</v>
       </c>
       <c r="F66" s="3">
         <v>2600</v>
       </c>
       <c r="G66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H66" s="3">
         <v>2500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2000</v>
-      </c>
-      <c r="R66" s="3">
-        <v>1300</v>
       </c>
       <c r="S66" s="3">
         <v>1300</v>
       </c>
       <c r="T66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U66" s="3">
         <v>1400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,8 +4289,11 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4136,50 +4309,53 @@
       <c r="G72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H72" s="3">
-        <v>-6300</v>
+      <c r="H72" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I72" s="3">
         <v>-6300</v>
       </c>
       <c r="J72" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="K72" s="3">
         <v>-5800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5100</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-4300</v>
       </c>
       <c r="M72" s="3">
         <v>-4300</v>
       </c>
       <c r="N72" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="O72" s="3">
         <v>-4400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E76" s="3">
         <v>22100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>19400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E81" s="3">
         <v>3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>100</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>200</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-100</v>
       </c>
       <c r="S81" s="3">
         <v>-100</v>
       </c>
       <c r="T81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U81" s="3">
         <v>6100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,19 +4816,20 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
@@ -4640,10 +4838,10 @@
         <v>200</v>
       </c>
       <c r="I83" s="3">
+        <v>200</v>
+      </c>
+      <c r="J83" s="3">
         <v>500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>200</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -4664,10 +4862,10 @@
         <v>200</v>
       </c>
       <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
         <v>300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>200</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
@@ -4678,8 +4876,11 @@
       <c r="U83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E89" s="3">
         <v>5100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>100</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>600</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>500</v>
       </c>
       <c r="R89" s="3">
         <v>500</v>
       </c>
       <c r="S89" s="3">
+        <v>500</v>
+      </c>
+      <c r="T89" s="3">
         <v>400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,8 +5274,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5067,7 +5287,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -5076,23 +5296,23 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2400</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -5103,19 +5323,22 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,46 +5458,49 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2400</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
       </c>
       <c r="O94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -5280,19 +5509,22 @@
         <v>0</v>
       </c>
       <c r="R94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S94" s="3">
         <v>-100</v>
       </c>
       <c r="T94" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="U94" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,31 +5546,32 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>-1400</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>-600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-600</v>
       </c>
       <c r="K96" s="3">
         <v>-600</v>
@@ -5347,7 +5580,7 @@
         <v>-600</v>
       </c>
       <c r="M96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5373,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,43 +5792,46 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1400</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
         <v>-700</v>
       </c>
       <c r="I100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J100" s="3">
         <v>-1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1100</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-600</v>
       </c>
       <c r="M100" s="3">
         <v>-600</v>
       </c>
       <c r="N100" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -5595,11 +5840,11 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>900</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -5609,8 +5854,11 @@
       <c r="U100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5618,113 +5866,119 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
-      </c>
-      <c r="O101" s="3">
-        <v>100</v>
       </c>
       <c r="P101" s="3">
         <v>100</v>
       </c>
       <c r="Q101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E102" s="3">
         <v>400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>AATC</t>
   </si>
@@ -656,164 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2600</v>
+        <v>3400</v>
       </c>
       <c r="E8" s="3">
         <v>3800</v>
       </c>
       <c r="F8" s="3">
-        <v>6700</v>
+        <v>3100</v>
       </c>
       <c r="G8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J8" s="3">
         <v>3100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="K8" s="3">
         <v>2400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="L8" s="3">
         <v>2700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <v>3500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <v>2800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>3200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>3300</v>
-      </c>
-      <c r="N8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="O8" s="3">
-        <v>3000</v>
-      </c>
-      <c r="P8" s="3">
-        <v>2900</v>
       </c>
       <c r="Q8" s="3">
         <v>3800</v>
       </c>
       <c r="R8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="S8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="T8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="U8" s="3">
         <v>3400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="V8" s="3">
         <v>3200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="W8" s="3">
         <v>3400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="X8" s="3">
         <v>3700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Y8" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -821,123 +842,141 @@
         <v>200</v>
       </c>
       <c r="E9" s="3">
+        <v>200</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
+        <v>200</v>
+      </c>
+      <c r="H9" s="3">
+        <v>100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>500</v>
+      </c>
+      <c r="J9" s="3">
+        <v>200</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L9" s="3">
+        <v>800</v>
+      </c>
+      <c r="M9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N9" s="3">
+        <v>600</v>
+      </c>
+      <c r="O9" s="3">
         <v>900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="P9" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>800</v>
+      </c>
+      <c r="R9" s="3">
+        <v>700</v>
+      </c>
+      <c r="S9" s="3">
+        <v>700</v>
+      </c>
+      <c r="T9" s="3">
         <v>900</v>
       </c>
-      <c r="H9" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I9" s="3">
-        <v>800</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="U9" s="3">
+        <v>600</v>
+      </c>
+      <c r="V9" s="3">
+        <v>600</v>
+      </c>
+      <c r="W9" s="3">
+        <v>600</v>
+      </c>
+      <c r="X9" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y9" s="3">
         <v>1200</v>
       </c>
-      <c r="K9" s="3">
-        <v>600</v>
-      </c>
-      <c r="L9" s="3">
-        <v>900</v>
-      </c>
-      <c r="M9" s="3">
-        <v>600</v>
-      </c>
-      <c r="N9" s="3">
-        <v>800</v>
-      </c>
-      <c r="O9" s="3">
-        <v>700</v>
-      </c>
-      <c r="P9" s="3">
-        <v>700</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>900</v>
-      </c>
-      <c r="R9" s="3">
-        <v>600</v>
-      </c>
-      <c r="S9" s="3">
-        <v>600</v>
-      </c>
-      <c r="T9" s="3">
-        <v>600</v>
-      </c>
-      <c r="U9" s="3">
-        <v>500</v>
-      </c>
-      <c r="V9" s="3">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G10" s="3">
         <v>2400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="H10" s="3">
         <v>3700</v>
       </c>
-      <c r="F10" s="3">
-        <v>5800</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N10" s="3">
         <v>2200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K10" s="3">
-        <v>2200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="M10" s="3">
-        <v>2700</v>
-      </c>
-      <c r="N10" s="3">
-        <v>3000</v>
       </c>
       <c r="O10" s="3">
         <v>2300</v>
       </c>
       <c r="P10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S10" s="3">
         <v>2200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="T10" s="3">
         <v>2900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="U10" s="3">
         <v>2800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="V10" s="3">
         <v>2600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="W10" s="3">
         <v>2800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="X10" s="3">
         <v>3200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Y10" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,8 +999,11 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -969,61 +1011,70 @@
         <v>600</v>
       </c>
       <c r="E12" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F12" s="3">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="G12" s="3">
         <v>600</v>
       </c>
       <c r="H12" s="3">
+        <v>700</v>
+      </c>
+      <c r="I12" s="3">
+        <v>700</v>
+      </c>
+      <c r="J12" s="3">
         <v>600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
+        <v>600</v>
+      </c>
+      <c r="M12" s="3">
         <v>1000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="N12" s="3">
         <v>400</v>
-      </c>
-      <c r="L12" s="3">
-        <v>500</v>
-      </c>
-      <c r="M12" s="3">
-        <v>600</v>
-      </c>
-      <c r="N12" s="3">
-        <v>500</v>
       </c>
       <c r="O12" s="3">
         <v>500</v>
       </c>
       <c r="P12" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>500</v>
+      </c>
+      <c r="R12" s="3">
+        <v>500</v>
+      </c>
+      <c r="S12" s="3">
         <v>800</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>800</v>
-      </c>
-      <c r="R12" s="3">
-        <v>800</v>
-      </c>
-      <c r="S12" s="3">
-        <v>900</v>
       </c>
       <c r="T12" s="3">
         <v>800</v>
       </c>
       <c r="U12" s="3">
+        <v>800</v>
+      </c>
+      <c r="V12" s="3">
+        <v>900</v>
+      </c>
+      <c r="W12" s="3">
+        <v>800</v>
+      </c>
+      <c r="X12" s="3">
         <v>700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="Y12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1084,8 +1135,17 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1095,8 +1155,8 @@
       <c r="E14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>17</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>17</v>
@@ -1113,8 +1173,8 @@
       <c r="K14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>17</v>
@@ -1123,17 +1183,17 @@
         <v>17</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R14" s="3">
         <v>-900</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1146,31 +1206,40 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1208,8 +1277,17 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1307,153 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2100</v>
+        <v>1700</v>
       </c>
       <c r="E17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F17" s="3">
         <v>2000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>4400</v>
       </c>
       <c r="G17" s="3">
         <v>2100</v>
       </c>
       <c r="H17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J17" s="3">
         <v>2100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L17" s="3">
         <v>1900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="M17" s="3">
         <v>4100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <v>2700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="O17" s="3">
         <v>3000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>2600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="Q17" s="3">
         <v>2900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="R17" s="3">
         <v>1600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="S17" s="3">
         <v>3000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>3100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <v>3000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
         <v>3400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="W17" s="3">
         <v>3500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="X17" s="3">
         <v>2800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Y17" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G18" s="3">
         <v>500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="H18" s="3">
         <v>1800</v>
       </c>
-      <c r="F18" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>900</v>
+      </c>
+      <c r="K18" s="3">
         <v>300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <v>100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="O18" s="3">
         <v>200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="R18" s="3">
         <v>1400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="T18" s="3">
         <v>700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="U18" s="3">
         <v>400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="X18" s="3">
         <v>900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Y18" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1377,35 +1476,38 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1439,70 +1541,88 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G21" s="3">
+        <v>700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K21" s="3">
+        <v>600</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N21" s="3">
+        <v>300</v>
+      </c>
+      <c r="O21" s="3">
+        <v>500</v>
+      </c>
+      <c r="P21" s="3">
         <v>900</v>
       </c>
-      <c r="E21" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F21" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="Q21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S21" s="3">
+        <v>100</v>
+      </c>
+      <c r="T21" s="3">
+        <v>900</v>
+      </c>
+      <c r="U21" s="3">
         <v>600</v>
       </c>
-      <c r="I21" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>300</v>
-      </c>
-      <c r="L21" s="3">
-        <v>500</v>
-      </c>
-      <c r="M21" s="3">
-        <v>900</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="V21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W21" s="3">
+        <v>100</v>
+      </c>
+      <c r="X21" s="3">
         <v>1100</v>
       </c>
-      <c r="O21" s="3">
-        <v>1600</v>
-      </c>
-      <c r="P21" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>900</v>
-      </c>
-      <c r="R21" s="3">
-        <v>600</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T21" s="3">
-        <v>100</v>
-      </c>
-      <c r="U21" s="3">
-        <v>1100</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="Y21" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1533,17 +1653,17 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>17</v>
@@ -1551,8 +1671,8 @@
       <c r="R22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>17</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>17</v>
@@ -1563,132 +1683,159 @@
       <c r="V22" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G23" s="3">
         <v>700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="H23" s="3">
         <v>1900</v>
       </c>
-      <c r="F23" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J23" s="3">
         <v>1000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="K23" s="3">
         <v>300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="P23" s="3">
         <v>700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="Q23" s="3">
         <v>900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="R23" s="3">
         <v>1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="T23" s="3">
         <v>600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="U23" s="3">
         <v>400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="X23" s="3">
         <v>900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Y23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-400</v>
+        <v>300</v>
       </c>
       <c r="E24" s="3">
         <v>400</v>
       </c>
       <c r="F24" s="3">
+        <v>300</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H24" s="3">
+        <v>400</v>
+      </c>
+      <c r="I24" s="3">
+        <v>300</v>
+      </c>
+      <c r="J24" s="3">
+        <v>200</v>
+      </c>
+      <c r="K24" s="3">
+        <v>200</v>
+      </c>
+      <c r="L24" s="3">
+        <v>100</v>
+      </c>
+      <c r="M24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="P24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>200</v>
-      </c>
-      <c r="I24" s="3">
-        <v>100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>500</v>
-      </c>
-      <c r="M24" s="3">
-        <v>100</v>
-      </c>
-      <c r="N24" s="3">
-        <v>200</v>
-      </c>
-      <c r="O24" s="3">
-        <v>200</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-500</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
       </c>
       <c r="R24" s="3">
         <v>200</v>
       </c>
       <c r="S24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>200</v>
+      </c>
+      <c r="V24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-5200</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1896,159 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="E26" s="3">
         <v>1500</v>
       </c>
       <c r="F26" s="3">
-        <v>1900</v>
+        <v>900</v>
       </c>
       <c r="G26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J26" s="3">
         <v>800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="K26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="L26" s="3">
         <v>600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="P26" s="3">
         <v>600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="Q26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="R26" s="3">
         <v>1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="S26" s="3">
         <v>400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="T26" s="3">
         <v>700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="U26" s="3">
         <v>200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="X26" s="3">
         <v>6100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Y26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="E27" s="3">
         <v>1500</v>
       </c>
       <c r="F27" s="3">
-        <v>1900</v>
+        <v>900</v>
       </c>
       <c r="G27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J27" s="3">
         <v>800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="K27" s="3">
         <v>100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="L27" s="3">
         <v>600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="P27" s="3">
         <v>600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="Q27" s="3">
         <v>800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="R27" s="3">
         <v>1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="S27" s="3">
         <v>400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="T27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="U27" s="3">
         <v>200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="X27" s="3">
         <v>6100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Y27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +2109,17 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1944,37 +2127,37 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>2100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>100</v>
       </c>
-      <c r="G29" s="3">
-        <v>100</v>
-      </c>
-      <c r="H29" s="3">
+      <c r="K29" s="3">
         <v>400</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>700</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -1997,8 +2180,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2251,17 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,35 +2322,44 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2183,70 +2393,88 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F33" s="3">
+        <v>900</v>
+      </c>
+      <c r="G33" s="3">
         <v>1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="H33" s="3">
         <v>3500</v>
       </c>
-      <c r="F33" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J33" s="3">
         <v>800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="K33" s="3">
         <v>500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="L33" s="3">
         <v>600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
         <v>100</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="P33" s="3">
         <v>600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="Q33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="R33" s="3">
         <v>1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="S33" s="3">
         <v>400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="T33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="U33" s="3">
         <v>200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="X33" s="3">
         <v>6100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Y33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2535,164 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F35" s="3">
+        <v>900</v>
+      </c>
+      <c r="G35" s="3">
         <v>1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="H35" s="3">
         <v>3500</v>
       </c>
-      <c r="F35" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J35" s="3">
         <v>800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="K35" s="3">
         <v>500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="L35" s="3">
         <v>600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="M35" s="3">
         <v>100</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="P35" s="3">
         <v>600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="Q35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="R35" s="3">
         <v>1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="S35" s="3">
         <v>400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="T35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="U35" s="3">
         <v>200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="X35" s="3">
         <v>6100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Y35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2715,11 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,106 +2742,118 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G41" s="3">
         <v>6500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>3300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>2900</v>
       </c>
-      <c r="G41" s="3">
-        <v>2300</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="3">
         <v>1200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>3400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>1900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>4400</v>
-      </c>
-      <c r="L41" s="3">
-        <v>8200</v>
-      </c>
-      <c r="M41" s="3">
-        <v>8500</v>
-      </c>
-      <c r="N41" s="3">
-        <v>8400</v>
       </c>
       <c r="O41" s="3">
         <v>8200</v>
       </c>
       <c r="P41" s="3">
+        <v>8500</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="R41" s="3">
+        <v>8200</v>
+      </c>
+      <c r="S41" s="3">
         <v>8600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="T41" s="3">
         <v>7500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="U41" s="3">
         <v>6800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="V41" s="3">
         <v>5400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="W41" s="3">
         <v>5100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="X41" s="3">
         <v>4700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Y41" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F42" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G42" s="3">
         <v>5900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="H42" s="3">
         <v>9200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="I42" s="3">
         <v>3200</v>
       </c>
-      <c r="G42" s="3">
-        <v>3300</v>
-      </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>3100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="L42" s="3">
         <v>700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="M42" s="3">
         <v>1200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="N42" s="3">
         <v>400</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>17</v>
       </c>
@@ -2593,14 +2863,14 @@
       <c r="Q42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2608,182 +2878,209 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F43" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G43" s="3">
         <v>3100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>4300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>4100</v>
       </c>
-      <c r="G43" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="3">
         <v>3700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>3700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>2800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>2500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>2400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>2500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>3500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="R43" s="3">
         <v>2900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="S43" s="3">
         <v>2300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="T43" s="3">
         <v>3200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="U43" s="3">
         <v>2600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="V43" s="3">
         <v>2900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="W43" s="3">
         <v>3100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="X43" s="3">
         <v>3400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Y43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E44" s="3">
         <v>2900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G44" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H44" s="3">
         <v>1700</v>
-      </c>
-      <c r="F44" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G44" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H44" s="3">
-        <v>2300</v>
       </c>
       <c r="I44" s="3">
         <v>2500</v>
       </c>
-      <c r="J44" s="3">
-        <v>1500</v>
+      <c r="J44" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K44" s="3">
-        <v>1400</v>
+        <v>2300</v>
       </c>
       <c r="L44" s="3">
-        <v>1400</v>
+        <v>2500</v>
       </c>
       <c r="M44" s="3">
         <v>1500</v>
       </c>
       <c r="N44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P44" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q44" s="3">
         <v>700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="R44" s="3">
         <v>800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="S44" s="3">
         <v>800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="T44" s="3">
         <v>400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="U44" s="3">
         <v>600</v>
-      </c>
-      <c r="S44" s="3">
-        <v>700</v>
-      </c>
-      <c r="T44" s="3">
-        <v>800</v>
-      </c>
-      <c r="U44" s="3">
-        <v>800</v>
       </c>
       <c r="V44" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>800</v>
+      </c>
+      <c r="X44" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>700</v>
-      </c>
-      <c r="E45" s="3">
-        <v>400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>300</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45" s="3">
         <v>500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1000</v>
       </c>
       <c r="L45" s="3">
         <v>400</v>
       </c>
       <c r="M45" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="N45" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="O45" s="3">
         <v>400</v>
       </c>
       <c r="P45" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>400</v>
+      </c>
+      <c r="R45" s="3">
+        <v>400</v>
+      </c>
+      <c r="S45" s="3">
         <v>500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>500</v>
-      </c>
-      <c r="R45" s="3">
-        <v>500</v>
-      </c>
-      <c r="S45" s="3">
-        <v>600</v>
       </c>
       <c r="T45" s="3">
         <v>500</v>
@@ -2792,108 +3089,126 @@
         <v>500</v>
       </c>
       <c r="V45" s="3">
+        <v>600</v>
+      </c>
+      <c r="W45" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F46" s="3">
+        <v>11600</v>
+      </c>
+      <c r="G46" s="3">
         <v>19100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>18900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>13100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46" s="3">
+        <v>10800</v>
+      </c>
+      <c r="L46" s="3">
+        <v>10600</v>
+      </c>
+      <c r="M46" s="3">
+        <v>8200</v>
+      </c>
+      <c r="N46" s="3">
+        <v>9600</v>
+      </c>
+      <c r="O46" s="3">
         <v>12400</v>
       </c>
-      <c r="H46" s="3">
-        <v>10800</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="P46" s="3">
+        <v>13100</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>13100</v>
+      </c>
+      <c r="R46" s="3">
+        <v>12300</v>
+      </c>
+      <c r="S46" s="3">
+        <v>12100</v>
+      </c>
+      <c r="T46" s="3">
+        <v>11600</v>
+      </c>
+      <c r="U46" s="3">
         <v>10600</v>
       </c>
-      <c r="J46" s="3">
-        <v>8200</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="V46" s="3">
         <v>9600</v>
       </c>
-      <c r="L46" s="3">
-        <v>12400</v>
-      </c>
-      <c r="M46" s="3">
-        <v>13100</v>
-      </c>
-      <c r="N46" s="3">
-        <v>13100</v>
-      </c>
-      <c r="O46" s="3">
-        <v>12300</v>
-      </c>
-      <c r="P46" s="3">
-        <v>12100</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>11600</v>
-      </c>
-      <c r="R46" s="3">
-        <v>10600</v>
-      </c>
-      <c r="S46" s="3">
-        <v>9600</v>
-      </c>
-      <c r="T46" s="3">
+      <c r="W46" s="3">
         <v>9500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="X46" s="3">
         <v>9400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Y46" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" s="3">
         <v>100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="H47" s="3">
         <v>100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="I47" s="3">
         <v>400</v>
       </c>
-      <c r="G47" s="3">
-        <v>900</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47" s="3">
         <v>1100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="L47" s="3">
         <v>1500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
         <v>3000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>2300</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>17</v>
       </c>
@@ -2903,14 +3218,14 @@
       <c r="Q47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -2918,132 +3233,159 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="E48" s="3">
         <v>2000</v>
       </c>
       <c r="F48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I48" s="3">
         <v>2100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K48" s="3">
         <v>2100</v>
       </c>
-      <c r="H48" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>2200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>2200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>2200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>2300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="R48" s="3">
         <v>400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="S48" s="3">
         <v>400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="T48" s="3">
         <v>500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="U48" s="3">
         <v>600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="V48" s="3">
         <v>600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="W48" s="3">
         <v>600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="X48" s="3">
         <v>700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Y48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>700</v>
+      </c>
+      <c r="F49" s="3">
+        <v>900</v>
+      </c>
+      <c r="G49" s="3">
         <v>1000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
         <v>1100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
         <v>2200</v>
       </c>
-      <c r="G49" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>2600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="L49" s="3">
         <v>2800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
         <v>3000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L49" s="3">
-        <v>2900</v>
-      </c>
-      <c r="M49" s="3">
-        <v>2800</v>
       </c>
       <c r="N49" s="3">
         <v>3000</v>
       </c>
       <c r="O49" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P49" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R49" s="3">
         <v>3100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="S49" s="3">
         <v>3200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="T49" s="3">
         <v>3300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="U49" s="3">
         <v>3500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="V49" s="3">
         <v>3700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="W49" s="3">
         <v>3900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="X49" s="3">
         <v>3900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="Y49" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3446,17 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,70 +3517,88 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>3500</v>
-      </c>
-      <c r="E52" s="3">
-        <v>2900</v>
-      </c>
-      <c r="F52" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>4200</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52" s="3">
         <v>4500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>4700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>4800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>4800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>4800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>5200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="Q52" s="3">
         <v>5400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="R52" s="3">
         <v>5500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="S52" s="3">
         <v>5700</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>5200</v>
-      </c>
-      <c r="R52" s="3">
-        <v>5200</v>
-      </c>
-      <c r="S52" s="3">
-        <v>5200</v>
       </c>
       <c r="T52" s="3">
         <v>5200</v>
       </c>
       <c r="U52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="V52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="W52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="X52" s="3">
         <v>5300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="Y52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3659,88 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>18500</v>
+      </c>
+      <c r="F54" s="3">
+        <v>17600</v>
+      </c>
+      <c r="G54" s="3">
         <v>25600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>25100</v>
-      </c>
-      <c r="F54" s="3">
-        <v>21800</v>
-      </c>
-      <c r="G54" s="3">
-        <v>22000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>21100</v>
       </c>
       <c r="I54" s="3">
         <v>21800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K54" s="3">
+        <v>21100</v>
+      </c>
+      <c r="L54" s="3">
+        <v>21800</v>
+      </c>
+      <c r="M54" s="3">
         <v>21200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>22000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>22400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>21300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>21700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="R54" s="3">
         <v>21300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="S54" s="3">
         <v>21400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="T54" s="3">
         <v>20700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="U54" s="3">
         <v>20000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="V54" s="3">
         <v>19100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="W54" s="3">
         <v>19200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="X54" s="3">
         <v>19200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Y54" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3763,11 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,49 +3790,52 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="3">
+        <v>100</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
-        <v>400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>500</v>
+      <c r="J57" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K57" s="3">
         <v>400</v>
       </c>
       <c r="L57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M57" s="3">
+        <v>500</v>
+      </c>
+      <c r="N57" s="3">
+        <v>400</v>
+      </c>
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>300</v>
-      </c>
-      <c r="O57" s="3">
-        <v>300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>500</v>
       </c>
       <c r="Q57" s="3">
         <v>300</v>
@@ -3451,19 +3844,28 @@
         <v>300</v>
       </c>
       <c r="S57" s="3">
+        <v>500</v>
+      </c>
+      <c r="T57" s="3">
+        <v>300</v>
+      </c>
+      <c r="U57" s="3">
+        <v>300</v>
+      </c>
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3486,7 +3888,7 @@
         <v>100</v>
       </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
@@ -3495,75 +3897,84 @@
         <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="T58" s="3">
         <v>600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="U58" s="3">
         <v>400</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
         <v>400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
+        <v>400</v>
+      </c>
+      <c r="G59" s="3">
+        <v>400</v>
+      </c>
+      <c r="H59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K59" s="3">
+        <v>400</v>
+      </c>
+      <c r="L59" s="3">
+        <v>400</v>
+      </c>
+      <c r="M59" s="3">
+        <v>400</v>
+      </c>
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
-        <v>400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>500</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
-      </c>
-      <c r="M59" s="3">
-        <v>600</v>
-      </c>
-      <c r="N59" s="3">
-        <v>700</v>
-      </c>
-      <c r="O59" s="3">
-        <v>500</v>
       </c>
       <c r="P59" s="3">
         <v>600</v>
@@ -3572,95 +3983,113 @@
         <v>700</v>
       </c>
       <c r="R59" s="3">
+        <v>500</v>
+      </c>
+      <c r="S59" s="3">
+        <v>600</v>
+      </c>
+      <c r="T59" s="3">
+        <v>700</v>
+      </c>
+      <c r="U59" s="3">
         <v>800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="V59" s="3">
         <v>700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="W59" s="3">
         <v>900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="X59" s="3">
         <v>1000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Y59" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>500</v>
+      </c>
+      <c r="F60" s="3">
+        <v>500</v>
+      </c>
+      <c r="G60" s="3">
         <v>1500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>1400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>1000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K60" s="3">
+        <v>900</v>
+      </c>
+      <c r="L60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M60" s="3">
         <v>1000</v>
-      </c>
-      <c r="H60" s="3">
-        <v>900</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K60" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L60" s="3">
-        <v>900</v>
-      </c>
-      <c r="M60" s="3">
-        <v>700</v>
       </c>
       <c r="N60" s="3">
         <v>1000</v>
       </c>
       <c r="O60" s="3">
+        <v>900</v>
+      </c>
+      <c r="P60" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R60" s="3">
         <v>800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="S60" s="3">
         <v>1500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="T60" s="3">
         <v>1500</v>
-      </c>
-      <c r="R60" s="3">
-        <v>1400</v>
-      </c>
-      <c r="S60" s="3">
-        <v>1300</v>
-      </c>
-      <c r="T60" s="3">
-        <v>1200</v>
       </c>
       <c r="U60" s="3">
         <v>1400</v>
       </c>
       <c r="V60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="W60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="E61" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="F61" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="G61" s="3">
         <v>1600</v>
@@ -3672,69 +4101,78 @@
         <v>1600</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>1600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N61" s="3">
         <v>1700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>1700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="T61" s="3">
         <v>400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="U61" s="3">
         <v>500</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3770,10 +4208,19 @@
         <v>0</v>
       </c>
       <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +4281,17 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4352,17 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4423,88 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G66" s="3">
         <v>3100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>3000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>2600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L66" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M66" s="3">
         <v>2600</v>
       </c>
-      <c r="H66" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I66" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="O66" s="3">
         <v>2600</v>
       </c>
-      <c r="K66" s="3">
-        <v>2700</v>
-      </c>
-      <c r="L66" s="3">
-        <v>2600</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>1000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="R66" s="3">
         <v>800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="S66" s="3">
         <v>2100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="T66" s="3">
         <v>1900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="U66" s="3">
         <v>2000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="V66" s="3">
         <v>1300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="W66" s="3">
         <v>1300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="X66" s="3">
         <v>1400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Y66" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4527,11 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4592,17 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4663,17 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4734,17 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,8 +4805,17 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4312,50 +4834,59 @@
       <c r="H72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L72" s="3">
         <v>-6300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>-6300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>-5800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>-5100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>-4300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>-4300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>-4400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="S72" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="T72" s="3">
         <v>-5900</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="T72" s="3">
-        <v>-6600</v>
       </c>
       <c r="U72" s="3">
         <v>-6500</v>
       </c>
       <c r="V72" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="W72" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="X72" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4947,17 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +5018,17 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +5089,88 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>16400</v>
+      </c>
+      <c r="F76" s="3">
+        <v>15600</v>
+      </c>
+      <c r="G76" s="3">
         <v>22500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>22100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>19200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K76" s="3">
+        <v>18600</v>
+      </c>
+      <c r="L76" s="3">
+        <v>18700</v>
+      </c>
+      <c r="M76" s="3">
+        <v>18600</v>
+      </c>
+      <c r="N76" s="3">
+        <v>19300</v>
+      </c>
+      <c r="O76" s="3">
+        <v>19800</v>
+      </c>
+      <c r="P76" s="3">
+        <v>20600</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>20700</v>
+      </c>
+      <c r="R76" s="3">
+        <v>20500</v>
+      </c>
+      <c r="S76" s="3">
         <v>19400</v>
       </c>
-      <c r="H76" s="3">
-        <v>18600</v>
-      </c>
-      <c r="I76" s="3">
-        <v>18700</v>
-      </c>
-      <c r="J76" s="3">
-        <v>18600</v>
-      </c>
-      <c r="K76" s="3">
-        <v>19300</v>
-      </c>
-      <c r="L76" s="3">
-        <v>19800</v>
-      </c>
-      <c r="M76" s="3">
-        <v>20600</v>
-      </c>
-      <c r="N76" s="3">
-        <v>20700</v>
-      </c>
-      <c r="O76" s="3">
-        <v>20500</v>
-      </c>
-      <c r="P76" s="3">
-        <v>19400</v>
-      </c>
-      <c r="Q76" s="3">
+      <c r="T76" s="3">
         <v>18800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="U76" s="3">
         <v>18000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="V76" s="3">
         <v>17800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="W76" s="3">
         <v>17900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="X76" s="3">
         <v>17800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Y76" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +5231,164 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F81" s="3">
+        <v>900</v>
+      </c>
+      <c r="G81" s="3">
         <v>1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="H81" s="3">
         <v>3500</v>
       </c>
-      <c r="F81" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J81" s="3">
         <v>800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="K81" s="3">
         <v>500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="L81" s="3">
         <v>600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="M81" s="3">
         <v>100</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="P81" s="3">
         <v>600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="Q81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="R81" s="3">
         <v>1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="S81" s="3">
         <v>400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="T81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="U81" s="3">
         <v>200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="X81" s="3">
         <v>6100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Y81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,31 +5411,34 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>500</v>
-      </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -4850,7 +5447,7 @@
         <v>200</v>
       </c>
       <c r="M83" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
@@ -4865,7 +5462,7 @@
         <v>200</v>
       </c>
       <c r="R83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
@@ -4874,13 +5471,22 @@
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>200</v>
+      </c>
+      <c r="X83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5547,17 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5618,17 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5689,17 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5760,17 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5831,88 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>-2200</v>
       </c>
-      <c r="E89" s="3">
-        <v>5100</v>
-      </c>
-      <c r="F89" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="3">
         <v>1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>100</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="S89" s="3">
         <v>1000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="T89" s="3">
         <v>600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="U89" s="3">
         <v>500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="V89" s="3">
         <v>500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="W89" s="3">
         <v>400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="X89" s="3">
         <v>900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="Y89" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,13 +5935,16 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -5292,53 +5955,62 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="O91" s="3">
         <v>-2400</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +6071,17 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +6142,88 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F94" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G94" s="3">
         <v>6900</v>
       </c>
-      <c r="E94" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="F94" s="3">
-        <v>600</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-4900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-3100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-2400</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="X94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="Y94" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,49 +6246,52 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1400</v>
+        <v>700</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F96" s="3">
-        <v>-1400</v>
+        <v>7900</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-1300</v>
+        <v>1400</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K96" s="3">
         <v>-600</v>
       </c>
       <c r="L96" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M96" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="N96" s="3">
         <v>-600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5609,8 +6311,17 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +6382,17 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +6453,17 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,190 +6524,226 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="G100" s="3">
         <v>-1400</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="L100" s="3">
         <v>-700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>-1300</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-600</v>
-      </c>
-      <c r="L100" s="3">
-        <v>1100</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-600</v>
       </c>
       <c r="N100" s="3">
         <v>-600</v>
       </c>
       <c r="O100" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="P100" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="Q100" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>900</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>100</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>300</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="G102" s="3">
         <v>3300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K102" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="L102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M102" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="N102" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="O102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P102" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>200</v>
+      </c>
+      <c r="R102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="S102" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T102" s="3">
+        <v>600</v>
+      </c>
+      <c r="U102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V102" s="3">
+        <v>300</v>
+      </c>
+      <c r="W102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G102" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I102" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M102" s="3">
-        <v>100</v>
-      </c>
-      <c r="N102" s="3">
-        <v>200</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-400</v>
-      </c>
-      <c r="P102" s="3">
-        <v>1100</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>600</v>
-      </c>
-      <c r="R102" s="3">
-        <v>1400</v>
-      </c>
-      <c r="S102" s="3">
-        <v>300</v>
-      </c>
-      <c r="T102" s="3">
-        <v>400</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="X102" s="3">
         <v>500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="Y102" s="3">
         <v>300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>AATC</t>
   </si>
@@ -656,185 +656,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E8" s="3">
         <v>3400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -845,52 +851,52 @@
         <v>200</v>
       </c>
       <c r="F9" s="3">
+        <v>200</v>
+      </c>
+      <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>800</v>
-      </c>
-      <c r="R9" s="3">
-        <v>700</v>
       </c>
       <c r="S9" s="3">
         <v>700</v>
       </c>
       <c r="T9" s="3">
+        <v>700</v>
+      </c>
+      <c r="U9" s="3">
         <v>900</v>
-      </c>
-      <c r="U9" s="3">
-        <v>600</v>
       </c>
       <c r="V9" s="3">
         <v>600</v>
@@ -899,13 +905,16 @@
         <v>600</v>
       </c>
       <c r="X9" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y9" s="3">
         <v>500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -913,70 +922,73 @@
         <v>3200</v>
       </c>
       <c r="E10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F10" s="3">
         <v>3600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,13 +1014,14 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E12" s="3">
         <v>600</v>
@@ -1020,13 +1033,13 @@
         <v>600</v>
       </c>
       <c r="H12" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I12" s="3">
         <v>700</v>
       </c>
       <c r="J12" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="K12" s="3">
         <v>600</v>
@@ -1035,25 +1048,25 @@
         <v>600</v>
       </c>
       <c r="M12" s="3">
+        <v>600</v>
+      </c>
+      <c r="N12" s="3">
         <v>1000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>600</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>500</v>
       </c>
       <c r="R12" s="3">
         <v>500</v>
       </c>
       <c r="S12" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="T12" s="3">
         <v>800</v>
@@ -1062,19 +1075,22 @@
         <v>800</v>
       </c>
       <c r="V12" s="3">
+        <v>800</v>
+      </c>
+      <c r="W12" s="3">
         <v>900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>800</v>
-      </c>
-      <c r="X12" s="3">
-        <v>700</v>
       </c>
       <c r="Y12" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1144,8 +1160,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1155,11 +1174,11 @@
       <c r="E14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>17</v>
+      <c r="F14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>17</v>
@@ -1182,21 +1201,21 @@
       <c r="N14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>17</v>
+      <c r="O14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S14" s="3">
         <v>-900</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1215,13 +1234,16 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1233,16 +1255,16 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>200</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1286,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2700</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2100</v>
       </c>
       <c r="K17" s="3">
         <v>2100</v>
       </c>
       <c r="L17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="M17" s="3">
         <v>1900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E18" s="3">
         <v>1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1479,8 +1511,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1494,11 +1527,11 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1506,11 +1539,11 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1550,79 +1583,85 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E21" s="3">
         <v>1800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1662,8 +1701,8 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>17</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>17</v>
@@ -1671,11 +1710,11 @@
       <c r="R22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>17</v>
+      <c r="S22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>17</v>
@@ -1692,150 +1731,159 @@
       <c r="Y22" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>200</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
       </c>
       <c r="L24" s="3">
+        <v>200</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>200</v>
       </c>
       <c r="R24" s="3">
         <v>200</v>
       </c>
       <c r="S24" s="3">
+        <v>200</v>
+      </c>
+      <c r="T24" s="3">
         <v>-500</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>800</v>
+      </c>
+      <c r="E26" s="3">
         <v>1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-600</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>200</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-100</v>
       </c>
       <c r="W26" s="3">
         <v>-100</v>
       </c>
       <c r="X26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y26" s="3">
         <v>6100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>800</v>
+      </c>
+      <c r="E27" s="3">
         <v>1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-600</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>200</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-100</v>
       </c>
       <c r="W27" s="3">
         <v>-100</v>
       </c>
       <c r="X27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y27" s="3">
         <v>6100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2136,31 +2196,31 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>2100</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>400</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>700</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2189,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,8 +2397,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2346,11 +2415,11 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -2358,11 +2427,11 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2402,79 +2471,85 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>800</v>
+      </c>
+      <c r="E33" s="3">
         <v>1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>100</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>200</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-100</v>
       </c>
       <c r="W33" s="3">
         <v>-100</v>
       </c>
       <c r="X33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y33" s="3">
         <v>6100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>800</v>
+      </c>
+      <c r="E35" s="3">
         <v>1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>100</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>200</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-100</v>
       </c>
       <c r="W35" s="3">
         <v>-100</v>
       </c>
       <c r="X35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y35" s="3">
         <v>6100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,118 +2830,122 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E41" s="3">
         <v>4300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2900</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E42" s="3">
         <v>2100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3200</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>3100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>400</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>17</v>
       </c>
@@ -2872,8 +2961,8 @@
       <c r="T42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2887,87 +2976,93 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="E43" s="3">
         <v>4200</v>
       </c>
       <c r="F43" s="3">
+        <v>4200</v>
+      </c>
+      <c r="G43" s="3">
         <v>3500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="3">
-        <v>3700</v>
+      <c r="K43" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L43" s="3">
         <v>3700</v>
       </c>
       <c r="M43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N43" s="3">
         <v>2800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E44" s="3">
         <v>2800</v>
-      </c>
-      <c r="E44" s="3">
-        <v>2900</v>
       </c>
       <c r="F44" s="3">
         <v>2900</v>
@@ -2976,61 +3071,64 @@
         <v>2900</v>
       </c>
       <c r="H44" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I44" s="3">
         <v>1700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2500</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L44" s="3">
         <v>2300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1500</v>
-      </c>
-      <c r="N44" s="3">
-        <v>1400</v>
       </c>
       <c r="O44" s="3">
         <v>1400</v>
       </c>
       <c r="P44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q44" s="3">
         <v>1500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>700</v>
-      </c>
-      <c r="R44" s="3">
-        <v>800</v>
       </c>
       <c r="S44" s="3">
         <v>800</v>
       </c>
       <c r="T44" s="3">
+        <v>800</v>
+      </c>
+      <c r="U44" s="3">
         <v>400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>700</v>
-      </c>
-      <c r="W44" s="3">
-        <v>800</v>
       </c>
       <c r="X44" s="3">
         <v>800</v>
       </c>
       <c r="Y44" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z44" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3055,32 +3153,32 @@
       <c r="J45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>400</v>
       </c>
       <c r="R45" s="3">
         <v>400</v>
       </c>
       <c r="S45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="T45" s="3">
         <v>500</v>
@@ -3089,10 +3187,10 @@
         <v>500</v>
       </c>
       <c r="V45" s="3">
+        <v>500</v>
+      </c>
+      <c r="W45" s="3">
         <v>600</v>
-      </c>
-      <c r="W45" s="3">
-        <v>500</v>
       </c>
       <c r="X45" s="3">
         <v>500</v>
@@ -3100,79 +3198,85 @@
       <c r="Y45" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E46" s="3">
         <v>14100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L46" s="3">
         <v>10800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12400</v>
-      </c>
-      <c r="P46" s="3">
-        <v>13100</v>
       </c>
       <c r="Q46" s="3">
         <v>13100</v>
       </c>
       <c r="R46" s="3">
+        <v>13100</v>
+      </c>
+      <c r="S46" s="3">
         <v>12300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3185,33 +3289,33 @@
       <c r="F47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="3">
-        <v>100</v>
+      <c r="G47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H47" s="3">
         <v>100</v>
       </c>
       <c r="I47" s="3">
+        <v>100</v>
+      </c>
+      <c r="J47" s="3">
         <v>400</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47" s="3">
         <v>1100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2300</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>17</v>
       </c>
@@ -3227,8 +3331,8 @@
       <c r="T47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3242,8 +3346,11 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3251,7 +3358,7 @@
         <v>2100</v>
       </c>
       <c r="E48" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="F48" s="3">
         <v>2000</v>
@@ -3263,16 +3370,16 @@
         <v>2000</v>
       </c>
       <c r="I48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J48" s="3">
         <v>2100</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L48" s="3">
         <v>2100</v>
-      </c>
-      <c r="L48" s="3">
-        <v>2200</v>
       </c>
       <c r="M48" s="3">
         <v>2200</v>
@@ -3281,25 +3388,25 @@
         <v>2200</v>
       </c>
       <c r="O48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P48" s="3">
         <v>2300</v>
-      </c>
-      <c r="P48" s="3">
-        <v>300</v>
       </c>
       <c r="Q48" s="3">
         <v>300</v>
       </c>
       <c r="R48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S48" s="3">
         <v>400</v>
       </c>
       <c r="T48" s="3">
+        <v>400</v>
+      </c>
+      <c r="U48" s="3">
         <v>500</v>
-      </c>
-      <c r="U48" s="3">
-        <v>600</v>
       </c>
       <c r="V48" s="3">
         <v>600</v>
@@ -3308,13 +3415,16 @@
         <v>600</v>
       </c>
       <c r="X48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Y48" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3322,70 +3432,73 @@
         <v>600</v>
       </c>
       <c r="E49" s="3">
+        <v>600</v>
+      </c>
+      <c r="F49" s="3">
         <v>700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2200</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>2600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2800</v>
-      </c>
-      <c r="M49" s="3">
-        <v>3000</v>
       </c>
       <c r="N49" s="3">
         <v>3000</v>
       </c>
       <c r="O49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P49" s="3">
         <v>2900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3700</v>
-      </c>
-      <c r="W49" s="3">
-        <v>3900</v>
       </c>
       <c r="X49" s="3">
         <v>3900</v>
       </c>
       <c r="Y49" s="3">
+        <v>3900</v>
+      </c>
+      <c r="Z49" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,8 +3642,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3552,14 +3671,14 @@
       <c r="J52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L52" s="3">
         <v>4500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4700</v>
-      </c>
-      <c r="M52" s="3">
-        <v>4800</v>
       </c>
       <c r="N52" s="3">
         <v>4800</v>
@@ -3568,19 +3687,19 @@
         <v>4800</v>
       </c>
       <c r="P52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Q52" s="3">
         <v>5200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5700</v>
-      </c>
-      <c r="T52" s="3">
-        <v>5200</v>
       </c>
       <c r="U52" s="3">
         <v>5200</v>
@@ -3592,13 +3711,16 @@
         <v>5200</v>
       </c>
       <c r="X52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="Y52" s="3">
         <v>5300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,8 +3790,11 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3677,70 +3802,73 @@
         <v>19200</v>
       </c>
       <c r="E54" s="3">
+        <v>19200</v>
+      </c>
+      <c r="F54" s="3">
         <v>18500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21800</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L54" s="3">
         <v>21100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>22400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>21300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>21400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>20700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>20000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>19100</v>
-      </c>
-      <c r="W54" s="3">
-        <v>19200</v>
       </c>
       <c r="X54" s="3">
         <v>19200</v>
       </c>
       <c r="Y54" s="3">
+        <v>19200</v>
+      </c>
+      <c r="Z54" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,70 +3922,71 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
       <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
-      </c>
-      <c r="O57" s="3">
-        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
       </c>
       <c r="Q57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R57" s="3">
         <v>300</v>
       </c>
       <c r="S57" s="3">
+        <v>300</v>
+      </c>
+      <c r="T57" s="3">
         <v>500</v>
-      </c>
-      <c r="T57" s="3">
-        <v>300</v>
       </c>
       <c r="U57" s="3">
         <v>300</v>
       </c>
       <c r="V57" s="3">
+        <v>300</v>
+      </c>
+      <c r="W57" s="3">
         <v>600</v>
-      </c>
-      <c r="W57" s="3">
-        <v>400</v>
       </c>
       <c r="X57" s="3">
         <v>400</v>
@@ -3864,8 +3994,11 @@
       <c r="Y57" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3888,10 +4021,10 @@
         <v>100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>100</v>
@@ -3906,7 +4039,7 @@
         <v>100</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3915,17 +4048,17 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>400</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>17</v>
       </c>
@@ -3935,8 +4068,11 @@
       <c r="Y58" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3944,7 +4080,7 @@
         <v>500</v>
       </c>
       <c r="E59" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F59" s="3">
         <v>400</v>
@@ -3953,16 +4089,16 @@
         <v>400</v>
       </c>
       <c r="H59" s="3">
+        <v>400</v>
+      </c>
+      <c r="I59" s="3">
         <v>1100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K59" s="3">
-        <v>400</v>
+      <c r="K59" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L59" s="3">
         <v>400</v>
@@ -3971,43 +4107,46 @@
         <v>400</v>
       </c>
       <c r="N59" s="3">
+        <v>400</v>
+      </c>
+      <c r="O59" s="3">
         <v>500</v>
-      </c>
-      <c r="O59" s="3">
-        <v>600</v>
       </c>
       <c r="P59" s="3">
         <v>600</v>
       </c>
       <c r="Q59" s="3">
+        <v>600</v>
+      </c>
+      <c r="R59" s="3">
         <v>700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4021,64 +4160,67 @@
         <v>500</v>
       </c>
       <c r="G60" s="3">
+        <v>500</v>
+      </c>
+      <c r="H60" s="3">
         <v>1500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L60" s="3">
         <v>900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1500</v>
-      </c>
-      <c r="M60" s="3">
-        <v>1000</v>
       </c>
       <c r="N60" s="3">
         <v>1000</v>
       </c>
       <c r="O60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P60" s="3">
         <v>900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>800</v>
-      </c>
-      <c r="S60" s="3">
-        <v>1500</v>
       </c>
       <c r="T60" s="3">
         <v>1500</v>
       </c>
       <c r="U60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V60" s="3">
         <v>1400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4092,7 +4234,7 @@
         <v>1500</v>
       </c>
       <c r="G61" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="H61" s="3">
         <v>1600</v>
@@ -4101,10 +4243,10 @@
         <v>1600</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K61" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>1600</v>
@@ -4113,13 +4255,13 @@
         <v>1600</v>
       </c>
       <c r="N61" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="O61" s="3">
         <v>1700</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -4128,17 +4270,17 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>500</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4148,8 +4290,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4174,8 +4319,8 @@
       <c r="J62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -4217,10 +4362,13 @@
         <v>0</v>
       </c>
       <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2100</v>
-      </c>
-      <c r="E66" s="3">
-        <v>2000</v>
       </c>
       <c r="F66" s="3">
         <v>2000</v>
       </c>
       <c r="G66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H66" s="3">
         <v>3100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2600</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L66" s="3">
         <v>2500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2000</v>
-      </c>
-      <c r="V66" s="3">
-        <v>1300</v>
       </c>
       <c r="W66" s="3">
         <v>1300</v>
       </c>
       <c r="X66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Y66" s="3">
         <v>1400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,8 +4984,11 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4843,50 +5016,53 @@
       <c r="K72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L72" s="3">
-        <v>-6300</v>
+      <c r="L72" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M72" s="3">
         <v>-6300</v>
       </c>
       <c r="N72" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="O72" s="3">
         <v>-5800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5100</v>
-      </c>
-      <c r="P72" s="3">
-        <v>-4300</v>
       </c>
       <c r="Q72" s="3">
         <v>-4300</v>
       </c>
       <c r="R72" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="S72" s="3">
         <v>-4400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E76" s="3">
         <v>17200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19200</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L76" s="3">
         <v>18600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>800</v>
+      </c>
+      <c r="E81" s="3">
         <v>1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>100</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>200</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-100</v>
       </c>
       <c r="W81" s="3">
         <v>-100</v>
       </c>
       <c r="X81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y81" s="3">
         <v>6100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,26 +5611,27 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>17</v>
+      <c r="D83" s="3">
+        <v>200</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>900</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
@@ -5441,16 +5639,16 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
       </c>
       <c r="M83" s="3">
+        <v>200</v>
+      </c>
+      <c r="N83" s="3">
         <v>500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
@@ -5471,10 +5669,10 @@
         <v>200</v>
       </c>
       <c r="U83" s="3">
+        <v>200</v>
+      </c>
+      <c r="V83" s="3">
         <v>300</v>
-      </c>
-      <c r="V83" s="3">
-        <v>200</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
@@ -5485,8 +5683,11 @@
       <c r="Y83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="3">
         <v>2000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1300</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>-2200</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K89" s="3">
         <v>1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>100</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
       <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>600</v>
-      </c>
-      <c r="U89" s="3">
-        <v>500</v>
       </c>
       <c r="V89" s="3">
         <v>500</v>
       </c>
       <c r="W89" s="3">
+        <v>500</v>
+      </c>
+      <c r="X89" s="3">
         <v>400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,25 +6157,26 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>17</v>
+      <c r="H91" s="3">
+        <v>0</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>17</v>
@@ -5964,30 +6184,30 @@
       <c r="J91" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2400</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -5998,19 +6218,22 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,58 +6377,61 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94" s="3">
         <v>1200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>6900</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2400</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -6211,19 +6440,22 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W94" s="3">
         <v>-100</v>
       </c>
       <c r="X94" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="Y94" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,43 +6481,44 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>700</v>
+      <c r="D96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E96" s="3">
         <v>700</v>
       </c>
       <c r="F96" s="3">
+        <v>700</v>
+      </c>
+      <c r="G96" s="3">
         <v>7900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1400</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L96" s="3">
         <v>-600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1300</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-600</v>
       </c>
       <c r="O96" s="3">
         <v>-600</v>
@@ -6294,7 +6527,7 @@
         <v>-600</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6320,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,55 +6775,58 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-700</v>
+      <c r="D100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E100" s="3">
         <v>-700</v>
       </c>
       <c r="F100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G100" s="3">
         <v>-7900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1400</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K100" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="L100" s="3">
         <v>-700</v>
       </c>
       <c r="M100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N100" s="3">
         <v>-1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1100</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-600</v>
       </c>
       <c r="Q100" s="3">
         <v>-600</v>
       </c>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
@@ -6590,11 +6835,11 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>900</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -6604,146 +6849,155 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>17</v>
+      <c r="D101" s="3">
+        <v>0</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3">
         <v>-100</v>
       </c>
       <c r="K101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
-      </c>
-      <c r="S101" s="3">
-        <v>100</v>
       </c>
       <c r="T101" s="3">
         <v>100</v>
       </c>
       <c r="U101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>2400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3300</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>AATC</t>
   </si>
@@ -656,196 +656,203 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E8" s="3">
         <v>3300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
         <v>200</v>
@@ -854,52 +861,52 @@
         <v>200</v>
       </c>
       <c r="G9" s="3">
+        <v>200</v>
+      </c>
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>800</v>
-      </c>
-      <c r="S9" s="3">
-        <v>700</v>
       </c>
       <c r="T9" s="3">
         <v>700</v>
       </c>
       <c r="U9" s="3">
+        <v>700</v>
+      </c>
+      <c r="V9" s="3">
         <v>900</v>
-      </c>
-      <c r="V9" s="3">
-        <v>600</v>
       </c>
       <c r="W9" s="3">
         <v>600</v>
@@ -908,87 +915,93 @@
         <v>600</v>
       </c>
       <c r="Y9" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z9" s="3">
         <v>500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3200</v>
+        <v>2200</v>
       </c>
       <c r="E10" s="3">
         <v>3200</v>
       </c>
       <c r="F10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G10" s="3">
         <v>3600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1024,7 +1038,7 @@
         <v>700</v>
       </c>
       <c r="E12" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F12" s="3">
         <v>600</v>
@@ -1036,13 +1050,13 @@
         <v>600</v>
       </c>
       <c r="I12" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="J12" s="3">
         <v>700</v>
       </c>
       <c r="K12" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L12" s="3">
         <v>600</v>
@@ -1051,25 +1065,25 @@
         <v>600</v>
       </c>
       <c r="N12" s="3">
+        <v>600</v>
+      </c>
+      <c r="O12" s="3">
         <v>1000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>600</v>
-      </c>
-      <c r="R12" s="3">
-        <v>500</v>
       </c>
       <c r="S12" s="3">
         <v>500</v>
       </c>
       <c r="T12" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="U12" s="3">
         <v>800</v>
@@ -1078,19 +1092,22 @@
         <v>800</v>
       </c>
       <c r="W12" s="3">
+        <v>800</v>
+      </c>
+      <c r="X12" s="3">
         <v>900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>800</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>700</v>
       </c>
       <c r="Z12" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1163,8 +1180,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1177,11 +1197,11 @@
       <c r="F14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>17</v>
+      <c r="G14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>17</v>
@@ -1204,21 +1224,21 @@
       <c r="O14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>17</v>
+      <c r="P14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="T14" s="3">
         <v>-900</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1237,8 +1257,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1246,7 +1269,7 @@
         <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>200</v>
@@ -1258,16 +1281,16 @@
         <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>200</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2700</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2100</v>
       </c>
       <c r="L17" s="3">
         <v>2100</v>
       </c>
       <c r="M17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N17" s="3">
         <v>1900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>400</v>
+      </c>
+      <c r="E18" s="3">
         <v>1500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1512,8 +1545,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1530,11 +1564,11 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1542,11 +1576,11 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1586,82 +1620,88 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>500</v>
+      </c>
+      <c r="E21" s="3">
         <v>1600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1704,8 +1744,8 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>17</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>17</v>
@@ -1713,11 +1753,11 @@
       <c r="S22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>17</v>
+      <c r="T22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>17</v>
@@ -1734,156 +1774,165 @@
       <c r="Z22" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
       <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
-      </c>
-      <c r="K24" s="3">
-        <v>200</v>
       </c>
       <c r="L24" s="3">
         <v>200</v>
       </c>
       <c r="M24" s="3">
+        <v>200</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
-      </c>
-      <c r="R24" s="3">
-        <v>200</v>
       </c>
       <c r="S24" s="3">
         <v>200</v>
       </c>
       <c r="T24" s="3">
+        <v>200</v>
+      </c>
+      <c r="U24" s="3">
         <v>-500</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>400</v>
+      </c>
+      <c r="E26" s="3">
         <v>800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-600</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>200</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-100</v>
       </c>
       <c r="X26" s="3">
         <v>-100</v>
       </c>
       <c r="Y26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z26" s="3">
         <v>6100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>400</v>
+      </c>
+      <c r="E27" s="3">
         <v>800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-600</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>200</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-100</v>
       </c>
       <c r="X27" s="3">
         <v>-100</v>
       </c>
       <c r="Y27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z27" s="3">
         <v>6100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2199,31 +2260,31 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>2100</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>400</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>700</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="P29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,8 +2467,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2418,11 +2488,11 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2430,11 +2500,11 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2474,82 +2544,88 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>400</v>
+      </c>
+      <c r="E33" s="3">
         <v>800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>100</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
       <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>200</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-100</v>
       </c>
       <c r="X33" s="3">
         <v>-100</v>
       </c>
       <c r="Y33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z33" s="3">
         <v>6100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>400</v>
+      </c>
+      <c r="E35" s="3">
         <v>800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>100</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
       <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>200</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-100</v>
       </c>
       <c r="X35" s="3">
         <v>-100</v>
       </c>
       <c r="Y35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z35" s="3">
         <v>6100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,124 +2917,128 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
         <v>4400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2900</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M41" s="3">
         <v>1200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E42" s="3">
         <v>3100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3200</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>3100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>400</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>17</v>
       </c>
@@ -2964,8 +3054,8 @@
       <c r="U42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -2979,82 +3069,88 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E43" s="3">
         <v>4100</v>
-      </c>
-      <c r="E43" s="3">
-        <v>4200</v>
       </c>
       <c r="F43" s="3">
         <v>4200</v>
       </c>
       <c r="G43" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H43" s="3">
         <v>3500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L43" s="3">
-        <v>3700</v>
+      <c r="L43" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M43" s="3">
         <v>3700</v>
       </c>
       <c r="N43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O43" s="3">
         <v>2800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3062,10 +3158,10 @@
         <v>2700</v>
       </c>
       <c r="E44" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F44" s="3">
         <v>2800</v>
-      </c>
-      <c r="F44" s="3">
-        <v>2900</v>
       </c>
       <c r="G44" s="3">
         <v>2900</v>
@@ -3074,61 +3170,64 @@
         <v>2900</v>
       </c>
       <c r="I44" s="3">
+        <v>2900</v>
+      </c>
+      <c r="J44" s="3">
         <v>1700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2500</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M44" s="3">
         <v>2300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1500</v>
-      </c>
-      <c r="O44" s="3">
-        <v>1400</v>
       </c>
       <c r="P44" s="3">
         <v>1400</v>
       </c>
       <c r="Q44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R44" s="3">
         <v>1500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>700</v>
-      </c>
-      <c r="S44" s="3">
-        <v>800</v>
       </c>
       <c r="T44" s="3">
         <v>800</v>
       </c>
       <c r="U44" s="3">
+        <v>800</v>
+      </c>
+      <c r="V44" s="3">
         <v>400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>700</v>
-      </c>
-      <c r="X44" s="3">
-        <v>800</v>
       </c>
       <c r="Y44" s="3">
         <v>800</v>
       </c>
       <c r="Z44" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA44" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3156,32 +3255,32 @@
       <c r="K45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
-      </c>
-      <c r="R45" s="3">
-        <v>400</v>
       </c>
       <c r="S45" s="3">
         <v>400</v>
       </c>
       <c r="T45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="U45" s="3">
         <v>500</v>
@@ -3190,10 +3289,10 @@
         <v>500</v>
       </c>
       <c r="W45" s="3">
+        <v>500</v>
+      </c>
+      <c r="X45" s="3">
         <v>600</v>
-      </c>
-      <c r="X45" s="3">
-        <v>500</v>
       </c>
       <c r="Y45" s="3">
         <v>500</v>
@@ -3201,82 +3300,88 @@
       <c r="Z45" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E46" s="3">
         <v>14600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13100</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M46" s="3">
         <v>10800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12400</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>13100</v>
       </c>
       <c r="R46" s="3">
         <v>13100</v>
       </c>
       <c r="S46" s="3">
+        <v>13100</v>
+      </c>
+      <c r="T46" s="3">
         <v>12300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3292,33 +3397,33 @@
       <c r="G47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H47" s="3">
-        <v>100</v>
+      <c r="H47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I47" s="3">
         <v>100</v>
       </c>
       <c r="J47" s="3">
+        <v>100</v>
+      </c>
+      <c r="K47" s="3">
         <v>400</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M47" s="3">
         <v>1100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2300</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>17</v>
       </c>
@@ -3334,8 +3439,8 @@
       <c r="U47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3349,8 +3454,11 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3361,7 +3469,7 @@
         <v>2100</v>
       </c>
       <c r="F48" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="G48" s="3">
         <v>2000</v>
@@ -3373,16 +3481,16 @@
         <v>2000</v>
       </c>
       <c r="J48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K48" s="3">
         <v>2100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M48" s="3">
         <v>2100</v>
-      </c>
-      <c r="M48" s="3">
-        <v>2200</v>
       </c>
       <c r="N48" s="3">
         <v>2200</v>
@@ -3391,25 +3499,25 @@
         <v>2200</v>
       </c>
       <c r="P48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q48" s="3">
         <v>2300</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>300</v>
       </c>
       <c r="R48" s="3">
         <v>300</v>
       </c>
       <c r="S48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="T48" s="3">
         <v>400</v>
       </c>
       <c r="U48" s="3">
+        <v>400</v>
+      </c>
+      <c r="V48" s="3">
         <v>500</v>
-      </c>
-      <c r="V48" s="3">
-        <v>600</v>
       </c>
       <c r="W48" s="3">
         <v>600</v>
@@ -3418,87 +3526,93 @@
         <v>600</v>
       </c>
       <c r="Y48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Z48" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E49" s="3">
         <v>600</v>
       </c>
       <c r="F49" s="3">
+        <v>600</v>
+      </c>
+      <c r="G49" s="3">
         <v>700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2200</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>2600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2800</v>
-      </c>
-      <c r="N49" s="3">
-        <v>3000</v>
       </c>
       <c r="O49" s="3">
         <v>3000</v>
       </c>
       <c r="P49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q49" s="3">
         <v>2900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3700</v>
-      </c>
-      <c r="X49" s="3">
-        <v>3900</v>
       </c>
       <c r="Y49" s="3">
         <v>3900</v>
       </c>
       <c r="Z49" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AA49" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,8 +3762,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3674,14 +3794,14 @@
       <c r="K52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M52" s="3">
         <v>4500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4700</v>
-      </c>
-      <c r="N52" s="3">
-        <v>4800</v>
       </c>
       <c r="O52" s="3">
         <v>4800</v>
@@ -3690,19 +3810,19 @@
         <v>4800</v>
       </c>
       <c r="Q52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="R52" s="3">
         <v>5200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5700</v>
-      </c>
-      <c r="U52" s="3">
-        <v>5200</v>
       </c>
       <c r="V52" s="3">
         <v>5200</v>
@@ -3714,13 +3834,16 @@
         <v>5200</v>
       </c>
       <c r="Y52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="Z52" s="3">
         <v>5300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>19200</v>
+        <v>13000</v>
       </c>
       <c r="E54" s="3">
         <v>19200</v>
       </c>
       <c r="F54" s="3">
+        <v>19200</v>
+      </c>
+      <c r="G54" s="3">
         <v>18500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21800</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M54" s="3">
         <v>21100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>22000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>21700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>21300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>20700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>20000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>19100</v>
-      </c>
-      <c r="X54" s="3">
-        <v>19200</v>
       </c>
       <c r="Y54" s="3">
         <v>19200</v>
       </c>
       <c r="Z54" s="3">
+        <v>19200</v>
+      </c>
+      <c r="AA54" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,73 +4053,74 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F57" s="3">
         <v>100</v>
       </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
-      </c>
-      <c r="P57" s="3">
-        <v>200</v>
       </c>
       <c r="Q57" s="3">
         <v>200</v>
       </c>
       <c r="R57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S57" s="3">
         <v>300</v>
       </c>
       <c r="T57" s="3">
+        <v>300</v>
+      </c>
+      <c r="U57" s="3">
         <v>500</v>
-      </c>
-      <c r="U57" s="3">
-        <v>300</v>
       </c>
       <c r="V57" s="3">
         <v>300</v>
       </c>
       <c r="W57" s="3">
+        <v>300</v>
+      </c>
+      <c r="X57" s="3">
         <v>600</v>
-      </c>
-      <c r="X57" s="3">
-        <v>400</v>
       </c>
       <c r="Y57" s="3">
         <v>400</v>
@@ -3997,8 +4128,11 @@
       <c r="Z57" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4024,10 +4158,10 @@
         <v>100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>100</v>
@@ -4042,7 +4176,7 @@
         <v>100</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -4051,17 +4185,17 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>400</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>17</v>
       </c>
@@ -4071,19 +4205,22 @@
       <c r="Z58" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
         <v>500</v>
       </c>
       <c r="F59" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G59" s="3">
         <v>400</v>
@@ -4092,16 +4229,16 @@
         <v>400</v>
       </c>
       <c r="I59" s="3">
+        <v>400</v>
+      </c>
+      <c r="J59" s="3">
         <v>1100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L59" s="3">
-        <v>400</v>
+      <c r="L59" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M59" s="3">
         <v>400</v>
@@ -4110,43 +4247,46 @@
         <v>400</v>
       </c>
       <c r="O59" s="3">
+        <v>400</v>
+      </c>
+      <c r="P59" s="3">
         <v>500</v>
-      </c>
-      <c r="P59" s="3">
-        <v>600</v>
       </c>
       <c r="Q59" s="3">
         <v>600</v>
       </c>
       <c r="R59" s="3">
+        <v>600</v>
+      </c>
+      <c r="S59" s="3">
         <v>700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4163,64 +4303,67 @@
         <v>500</v>
       </c>
       <c r="H60" s="3">
+        <v>500</v>
+      </c>
+      <c r="I60" s="3">
         <v>1500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M60" s="3">
         <v>900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1500</v>
-      </c>
-      <c r="N60" s="3">
-        <v>1000</v>
       </c>
       <c r="O60" s="3">
         <v>1000</v>
       </c>
       <c r="P60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q60" s="3">
         <v>900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>800</v>
-      </c>
-      <c r="T60" s="3">
-        <v>1500</v>
       </c>
       <c r="U60" s="3">
         <v>1500</v>
       </c>
       <c r="V60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W60" s="3">
         <v>1400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4237,7 +4380,7 @@
         <v>1500</v>
       </c>
       <c r="H61" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="I61" s="3">
         <v>1600</v>
@@ -4246,10 +4389,10 @@
         <v>1600</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="L61" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3">
         <v>1600</v>
@@ -4258,13 +4401,13 @@
         <v>1600</v>
       </c>
       <c r="O61" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="P61" s="3">
         <v>1700</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -4273,17 +4416,17 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>500</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4293,8 +4436,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4322,8 +4468,8 @@
       <c r="K62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -4365,10 +4511,13 @@
         <v>0</v>
       </c>
       <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,8 +4744,11 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4598,73 +4756,76 @@
         <v>2000</v>
       </c>
       <c r="E66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F66" s="3">
         <v>2100</v>
-      </c>
-      <c r="F66" s="3">
-        <v>2000</v>
       </c>
       <c r="G66" s="3">
         <v>2000</v>
       </c>
       <c r="H66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I66" s="3">
         <v>3100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2600</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M66" s="3">
         <v>2500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2000</v>
-      </c>
-      <c r="W66" s="3">
-        <v>1300</v>
       </c>
       <c r="X66" s="3">
         <v>1300</v>
       </c>
       <c r="Y66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Z66" s="3">
         <v>1400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,8 +5158,11 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5019,50 +5193,53 @@
       <c r="L72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M72" s="3">
-        <v>-6300</v>
+      <c r="M72" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N72" s="3">
         <v>-6300</v>
       </c>
       <c r="O72" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="P72" s="3">
         <v>-5800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5100</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-4300</v>
       </c>
       <c r="R72" s="3">
         <v>-4300</v>
       </c>
       <c r="S72" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="T72" s="3">
         <v>-4400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E76" s="3">
         <v>17100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19200</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M76" s="3">
         <v>18600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>20500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>400</v>
+      </c>
+      <c r="E81" s="3">
         <v>800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>100</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
       <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>200</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-100</v>
       </c>
       <c r="X81" s="3">
         <v>-100</v>
       </c>
       <c r="Y81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z81" s="3">
         <v>6100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,29 +5810,30 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>17</v>
+      <c r="E83" s="3">
+        <v>200</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>900</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
@@ -5642,16 +5841,16 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>200</v>
       </c>
       <c r="N83" s="3">
+        <v>200</v>
+      </c>
+      <c r="O83" s="3">
         <v>500</v>
-      </c>
-      <c r="O83" s="3">
-        <v>200</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
@@ -5672,10 +5871,10 @@
         <v>200</v>
       </c>
       <c r="V83" s="3">
+        <v>200</v>
+      </c>
+      <c r="W83" s="3">
         <v>300</v>
-      </c>
-      <c r="W83" s="3">
-        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
@@ -5686,8 +5885,11 @@
       <c r="Z83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F89" s="3">
         <v>2000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1300</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>-2200</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L89" s="3">
         <v>1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>1100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>600</v>
-      </c>
-      <c r="V89" s="3">
-        <v>500</v>
       </c>
       <c r="W89" s="3">
         <v>500</v>
       </c>
       <c r="X89" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y89" s="3">
         <v>400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,19 +6378,20 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="D91" s="3">
         <v>-100</v>
       </c>
+      <c r="E91" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -6178,8 +6399,8 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>17</v>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>17</v>
@@ -6187,30 +6408,30 @@
       <c r="K91" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -6221,19 +6442,22 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,61 +6607,64 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F94" s="3">
         <v>1200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>6900</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L94" s="3">
         <v>100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S94" s="3">
         <v>-100</v>
       </c>
       <c r="T94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -6443,19 +6673,22 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X94" s="3">
         <v>-100</v>
       </c>
       <c r="Y94" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="Z94" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,46 +6715,47 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E96" s="3">
-        <v>700</v>
+      <c r="D96" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F96" s="3">
         <v>700</v>
       </c>
       <c r="G96" s="3">
+        <v>700</v>
+      </c>
+      <c r="H96" s="3">
         <v>7900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1400</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M96" s="3">
         <v>-600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-600</v>
       </c>
       <c r="P96" s="3">
         <v>-600</v>
@@ -6530,7 +6764,7 @@
         <v>-600</v>
       </c>
       <c r="R96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,58 +7021,61 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-700</v>
+      <c r="D100" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F100" s="3">
         <v>-700</v>
       </c>
       <c r="G100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H100" s="3">
         <v>-7900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1400</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L100" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="M100" s="3">
         <v>-700</v>
       </c>
       <c r="N100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="O100" s="3">
         <v>-1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-600</v>
       </c>
       <c r="R100" s="3">
         <v>-600</v>
       </c>
       <c r="S100" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -6838,11 +7084,11 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>900</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -6852,152 +7098,161 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>17</v>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="G101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
       </c>
       <c r="L101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-100</v>
-      </c>
-      <c r="T101" s="3">
-        <v>100</v>
       </c>
       <c r="U101" s="3">
         <v>100</v>
       </c>
       <c r="V101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-3700</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>2400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3300</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AATC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="92">
   <si>
     <t>AATC</t>
   </si>
@@ -656,260 +656,267 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>2200</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="N8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="O8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="P8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="R8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S8" s="3">
         <v>3300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="T8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="U8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="V8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="W8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="X8" s="3">
         <v>3400</v>
       </c>
-      <c r="G8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="H8" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="K8" s="3">
-        <v>4000</v>
-      </c>
-      <c r="L8" s="3">
-        <v>3100</v>
-      </c>
-      <c r="M8" s="3">
-        <v>2400</v>
-      </c>
-      <c r="N8" s="3">
-        <v>2700</v>
-      </c>
-      <c r="O8" s="3">
-        <v>3500</v>
-      </c>
-      <c r="P8" s="3">
-        <v>2800</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="Y8" s="3">
         <v>3200</v>
       </c>
-      <c r="R8" s="3">
-        <v>3300</v>
-      </c>
-      <c r="S8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="T8" s="3">
-        <v>3000</v>
-      </c>
-      <c r="U8" s="3">
-        <v>2900</v>
-      </c>
-      <c r="V8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="Z8" s="3">
         <v>3400</v>
       </c>
-      <c r="X8" s="3">
-        <v>3200</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>3400</v>
-      </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="3">
+        <v>100</v>
+      </c>
+      <c r="L9" s="3">
+        <v>500</v>
+      </c>
+      <c r="M9" s="3">
         <v>200</v>
       </c>
-      <c r="F9" s="3">
-        <v>200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>100</v>
-      </c>
-      <c r="I9" s="3">
-        <v>200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>100</v>
-      </c>
-      <c r="K9" s="3">
-        <v>500</v>
-      </c>
-      <c r="L9" s="3">
-        <v>200</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>800</v>
-      </c>
-      <c r="T9" s="3">
-        <v>700</v>
       </c>
       <c r="U9" s="3">
         <v>700</v>
       </c>
       <c r="V9" s="3">
+        <v>700</v>
+      </c>
+      <c r="W9" s="3">
         <v>900</v>
-      </c>
-      <c r="W9" s="3">
-        <v>600</v>
       </c>
       <c r="X9" s="3">
         <v>600</v>
@@ -918,90 +925,96 @@
         <v>600</v>
       </c>
       <c r="Z9" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA9" s="3">
         <v>500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L10" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Q10" s="3">
         <v>2200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="R10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="T10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="U10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="V10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="W10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="X10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AA10" s="3">
         <v>3200</v>
       </c>
-      <c r="F10" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="AB10" s="3">
         <v>3000</v>
       </c>
-      <c r="I10" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J10" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K10" s="3">
-        <v>3500</v>
-      </c>
-      <c r="L10" s="3">
-        <v>2900</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1300</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1900</v>
-      </c>
-      <c r="O10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="P10" s="3">
-        <v>2200</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="R10" s="3">
-        <v>2700</v>
-      </c>
-      <c r="S10" s="3">
-        <v>3000</v>
-      </c>
-      <c r="T10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="U10" s="3">
-        <v>2200</v>
-      </c>
-      <c r="V10" s="3">
-        <v>2900</v>
-      </c>
-      <c r="W10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="X10" s="3">
-        <v>2600</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>3200</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,37 +1042,38 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>700</v>
-      </c>
-      <c r="E12" s="3">
-        <v>700</v>
-      </c>
-      <c r="F12" s="3">
-        <v>600</v>
-      </c>
-      <c r="G12" s="3">
-        <v>600</v>
-      </c>
-      <c r="H12" s="3">
-        <v>600</v>
-      </c>
-      <c r="I12" s="3">
-        <v>600</v>
-      </c>
-      <c r="J12" s="3">
-        <v>700</v>
+      <c r="D12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K12" s="3">
         <v>700</v>
       </c>
       <c r="L12" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M12" s="3">
         <v>600</v>
@@ -1068,25 +1082,25 @@
         <v>600</v>
       </c>
       <c r="O12" s="3">
+        <v>600</v>
+      </c>
+      <c r="P12" s="3">
         <v>1000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>600</v>
-      </c>
-      <c r="S12" s="3">
-        <v>500</v>
       </c>
       <c r="T12" s="3">
         <v>500</v>
       </c>
       <c r="U12" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="V12" s="3">
         <v>800</v>
@@ -1095,19 +1109,22 @@
         <v>800</v>
       </c>
       <c r="X12" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y12" s="3">
         <v>900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>800</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>700</v>
       </c>
       <c r="AA12" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1183,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1200,8 +1220,8 @@
       <c r="G14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>17</v>
@@ -1227,21 +1247,21 @@
       <c r="P14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>17</v>
+      <c r="Q14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="U14" s="3">
         <v>-900</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1260,40 +1280,43 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
       <c r="K15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>200</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3">
-        <v>1700</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2700</v>
-      </c>
-      <c r="L17" s="3">
-        <v>2100</v>
       </c>
       <c r="M17" s="3">
         <v>2100</v>
       </c>
       <c r="N17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O17" s="3">
         <v>1900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M18" s="3">
+        <v>900</v>
+      </c>
+      <c r="N18" s="3">
+        <v>300</v>
+      </c>
+      <c r="O18" s="3">
+        <v>800</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>100</v>
+      </c>
+      <c r="R18" s="3">
+        <v>200</v>
+      </c>
+      <c r="S18" s="3">
+        <v>700</v>
+      </c>
+      <c r="T18" s="3">
+        <v>900</v>
+      </c>
+      <c r="U18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W18" s="3">
+        <v>700</v>
+      </c>
+      <c r="X18" s="3">
         <v>400</v>
       </c>
-      <c r="E18" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="Y18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA18" s="3">
         <v>900</v>
       </c>
-      <c r="M18" s="3">
-        <v>300</v>
-      </c>
-      <c r="N18" s="3">
-        <v>800</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="P18" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>200</v>
-      </c>
-      <c r="R18" s="3">
-        <v>700</v>
-      </c>
-      <c r="S18" s="3">
-        <v>900</v>
-      </c>
-      <c r="T18" s="3">
-        <v>1400</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V18" s="3">
-        <v>700</v>
-      </c>
-      <c r="W18" s="3">
-        <v>400</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>900</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1546,31 +1579,32 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1579,11 +1613,11 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1623,108 +1657,114 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N21" s="3">
+        <v>600</v>
+      </c>
+      <c r="O21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>300</v>
+      </c>
+      <c r="R21" s="3">
         <v>500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="S21" s="3">
+        <v>900</v>
+      </c>
+      <c r="T21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U21" s="3">
         <v>1600</v>
       </c>
-      <c r="F21" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G21" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>700</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K21" s="3">
-        <v>1600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="V21" s="3">
+        <v>100</v>
+      </c>
+      <c r="W21" s="3">
+        <v>900</v>
+      </c>
+      <c r="X21" s="3">
         <v>600</v>
       </c>
-      <c r="N21" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P21" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>500</v>
-      </c>
-      <c r="R21" s="3">
-        <v>900</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="Y21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA21" s="3">
         <v>1100</v>
       </c>
-      <c r="T21" s="3">
-        <v>1600</v>
-      </c>
-      <c r="U21" s="3">
-        <v>100</v>
-      </c>
-      <c r="V21" s="3">
-        <v>900</v>
-      </c>
-      <c r="W21" s="3">
-        <v>600</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1747,8 +1787,8 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>17</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>17</v>
@@ -1756,11 +1796,11 @@
       <c r="T22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>17</v>
+      <c r="U22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>17</v>
@@ -1777,162 +1817,171 @@
       <c r="AA22" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>500</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G23" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N23" s="3">
+        <v>300</v>
+      </c>
+      <c r="O23" s="3">
+        <v>800</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
+        <v>300</v>
+      </c>
+      <c r="S23" s="3">
         <v>700</v>
       </c>
-      <c r="J23" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K23" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L23" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M23" s="3">
-        <v>300</v>
-      </c>
-      <c r="N23" s="3">
-        <v>800</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-700</v>
-      </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>300</v>
-      </c>
-      <c r="R23" s="3">
-        <v>700</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>100</v>
-      </c>
-      <c r="E24" s="3">
-        <v>800</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="3">
+        <v>400</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>400</v>
-      </c>
-      <c r="H24" s="3">
-        <v>300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J24" s="3">
-        <v>400</v>
-      </c>
-      <c r="K24" s="3">
-        <v>300</v>
-      </c>
-      <c r="L24" s="3">
-        <v>200</v>
       </c>
       <c r="M24" s="3">
         <v>200</v>
       </c>
       <c r="N24" s="3">
+        <v>200</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
-      </c>
-      <c r="S24" s="3">
-        <v>200</v>
       </c>
       <c r="T24" s="3">
         <v>200</v>
       </c>
       <c r="U24" s="3">
+        <v>200</v>
+      </c>
+      <c r="V24" s="3">
         <v>-500</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M26" s="3">
+        <v>800</v>
+      </c>
+      <c r="N26" s="3">
+        <v>100</v>
+      </c>
+      <c r="O26" s="3">
+        <v>600</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S26" s="3">
+        <v>600</v>
+      </c>
+      <c r="T26" s="3">
+        <v>800</v>
+      </c>
+      <c r="U26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V26" s="3">
         <v>400</v>
       </c>
-      <c r="E26" s="3">
-        <v>800</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>900</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L26" s="3">
-        <v>800</v>
-      </c>
-      <c r="M26" s="3">
-        <v>100</v>
-      </c>
-      <c r="N26" s="3">
-        <v>600</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-600</v>
-      </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R26" s="3">
-        <v>600</v>
-      </c>
-      <c r="S26" s="3">
-        <v>800</v>
-      </c>
-      <c r="T26" s="3">
-        <v>1100</v>
-      </c>
-      <c r="U26" s="3">
-        <v>400</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>200</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-100</v>
       </c>
       <c r="Y26" s="3">
         <v>-100</v>
       </c>
       <c r="Z26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA26" s="3">
         <v>6100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M27" s="3">
+        <v>800</v>
+      </c>
+      <c r="N27" s="3">
+        <v>100</v>
+      </c>
+      <c r="O27" s="3">
+        <v>600</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S27" s="3">
+        <v>600</v>
+      </c>
+      <c r="T27" s="3">
+        <v>800</v>
+      </c>
+      <c r="U27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V27" s="3">
         <v>400</v>
       </c>
-      <c r="E27" s="3">
-        <v>800</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J27" s="3">
-        <v>3500</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L27" s="3">
-        <v>800</v>
-      </c>
-      <c r="M27" s="3">
-        <v>100</v>
-      </c>
-      <c r="N27" s="3">
-        <v>600</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-600</v>
-      </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R27" s="3">
-        <v>600</v>
-      </c>
-      <c r="S27" s="3">
-        <v>800</v>
-      </c>
-      <c r="T27" s="3">
-        <v>1100</v>
-      </c>
-      <c r="U27" s="3">
-        <v>400</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>200</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-100</v>
       </c>
       <c r="Y27" s="3">
         <v>-100</v>
       </c>
       <c r="Z27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA27" s="3">
         <v>6100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2263,31 +2324,31 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>2100</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>400</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>700</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Q29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,31 +2537,34 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2503,11 +2573,11 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2547,85 +2617,91 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M33" s="3">
+        <v>800</v>
+      </c>
+      <c r="N33" s="3">
+        <v>500</v>
+      </c>
+      <c r="O33" s="3">
+        <v>600</v>
+      </c>
+      <c r="P33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S33" s="3">
+        <v>600</v>
+      </c>
+      <c r="T33" s="3">
+        <v>800</v>
+      </c>
+      <c r="U33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V33" s="3">
         <v>400</v>
       </c>
-      <c r="E33" s="3">
-        <v>800</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>900</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J33" s="3">
-        <v>3500</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L33" s="3">
-        <v>800</v>
-      </c>
-      <c r="M33" s="3">
-        <v>500</v>
-      </c>
-      <c r="N33" s="3">
-        <v>600</v>
-      </c>
-      <c r="O33" s="3">
-        <v>100</v>
-      </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R33" s="3">
-        <v>600</v>
-      </c>
-      <c r="S33" s="3">
-        <v>800</v>
-      </c>
-      <c r="T33" s="3">
-        <v>1100</v>
-      </c>
-      <c r="U33" s="3">
-        <v>400</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>200</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-100</v>
       </c>
       <c r="Y33" s="3">
         <v>-100</v>
       </c>
       <c r="Z33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA33" s="3">
         <v>6100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M35" s="3">
+        <v>800</v>
+      </c>
+      <c r="N35" s="3">
+        <v>500</v>
+      </c>
+      <c r="O35" s="3">
+        <v>600</v>
+      </c>
+      <c r="P35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S35" s="3">
+        <v>600</v>
+      </c>
+      <c r="T35" s="3">
+        <v>800</v>
+      </c>
+      <c r="U35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V35" s="3">
         <v>400</v>
       </c>
-      <c r="E35" s="3">
-        <v>800</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>900</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J35" s="3">
-        <v>3500</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L35" s="3">
-        <v>800</v>
-      </c>
-      <c r="M35" s="3">
-        <v>500</v>
-      </c>
-      <c r="N35" s="3">
-        <v>600</v>
-      </c>
-      <c r="O35" s="3">
-        <v>100</v>
-      </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R35" s="3">
-        <v>600</v>
-      </c>
-      <c r="S35" s="3">
-        <v>800</v>
-      </c>
-      <c r="T35" s="3">
-        <v>1100</v>
-      </c>
-      <c r="U35" s="3">
-        <v>400</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>200</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-100</v>
       </c>
       <c r="Y35" s="3">
         <v>-100</v>
       </c>
       <c r="Z35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA35" s="3">
         <v>6100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,130 +3004,134 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>600</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L41" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="P41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q41" s="3">
         <v>4400</v>
       </c>
-      <c r="F41" s="3">
-        <v>4300</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H41" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I41" s="3">
-        <v>6500</v>
-      </c>
-      <c r="J41" s="3">
-        <v>3300</v>
-      </c>
-      <c r="K41" s="3">
-        <v>2900</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M41" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N41" s="3">
-        <v>3400</v>
-      </c>
-      <c r="O41" s="3">
-        <v>1900</v>
-      </c>
-      <c r="P41" s="3">
-        <v>4400</v>
-      </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>9200</v>
+      </c>
+      <c r="L42" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>3100</v>
       </c>
-      <c r="F42" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G42" s="3">
-        <v>3400</v>
-      </c>
-      <c r="H42" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I42" s="3">
-        <v>5900</v>
-      </c>
-      <c r="J42" s="3">
-        <v>9200</v>
-      </c>
-      <c r="K42" s="3">
-        <v>3200</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>3100</v>
-      </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>400</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>17</v>
       </c>
@@ -3057,8 +3147,8 @@
       <c r="V42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3072,162 +3162,171 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>3700</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="3">
+        <v>4300</v>
+      </c>
+      <c r="L43" s="3">
         <v>4100</v>
       </c>
-      <c r="F43" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G43" s="3">
-        <v>4200</v>
-      </c>
-      <c r="H43" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>3100</v>
-      </c>
-      <c r="J43" s="3">
-        <v>4300</v>
-      </c>
-      <c r="K43" s="3">
-        <v>4100</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M43" s="3">
-        <v>3700</v>
+      <c r="M43" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N43" s="3">
         <v>3700</v>
       </c>
       <c r="O43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="P43" s="3">
         <v>2800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>2700</v>
-      </c>
-      <c r="E44" s="3">
-        <v>2700</v>
-      </c>
-      <c r="F44" s="3">
-        <v>2800</v>
-      </c>
-      <c r="G44" s="3">
-        <v>2900</v>
-      </c>
-      <c r="H44" s="3">
-        <v>2900</v>
-      </c>
-      <c r="I44" s="3">
-        <v>2900</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="3">
         <v>1700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2500</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N44" s="3">
         <v>2300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1500</v>
-      </c>
-      <c r="P44" s="3">
-        <v>1400</v>
       </c>
       <c r="Q44" s="3">
         <v>1400</v>
       </c>
       <c r="R44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S44" s="3">
         <v>1500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>700</v>
-      </c>
-      <c r="T44" s="3">
-        <v>800</v>
       </c>
       <c r="U44" s="3">
         <v>800</v>
       </c>
       <c r="V44" s="3">
+        <v>800</v>
+      </c>
+      <c r="W44" s="3">
         <v>400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>700</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>800</v>
       </c>
       <c r="Z44" s="3">
         <v>800</v>
       </c>
       <c r="AA44" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB44" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3258,32 +3357,32 @@
       <c r="L45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
-      </c>
-      <c r="S45" s="3">
-        <v>400</v>
       </c>
       <c r="T45" s="3">
         <v>400</v>
       </c>
       <c r="U45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="V45" s="3">
         <v>500</v>
@@ -3292,10 +3391,10 @@
         <v>500</v>
       </c>
       <c r="X45" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y45" s="3">
         <v>600</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>500</v>
       </c>
       <c r="Z45" s="3">
         <v>500</v>
@@ -3303,85 +3402,91 @@
       <c r="AA45" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>8500</v>
-      </c>
-      <c r="E46" s="3">
-        <v>14600</v>
-      </c>
-      <c r="F46" s="3">
-        <v>14100</v>
-      </c>
-      <c r="G46" s="3">
-        <v>13000</v>
-      </c>
-      <c r="H46" s="3">
-        <v>11600</v>
-      </c>
-      <c r="I46" s="3">
-        <v>19100</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46" s="3">
         <v>18900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" s="3">
         <v>10800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12400</v>
-      </c>
-      <c r="R46" s="3">
-        <v>13100</v>
       </c>
       <c r="S46" s="3">
         <v>13100</v>
       </c>
       <c r="T46" s="3">
+        <v>13100</v>
+      </c>
+      <c r="U46" s="3">
         <v>12300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3400,33 +3505,33 @@
       <c r="H47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47" s="3">
         <v>100</v>
       </c>
-      <c r="J47" s="3">
-        <v>100</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>400</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" s="3">
         <v>1100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2300</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>17</v>
       </c>
@@ -3442,8 +3547,8 @@
       <c r="V47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3457,43 +3562,46 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L48" s="3">
         <v>2100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N48" s="3">
         <v>2100</v>
-      </c>
-      <c r="F48" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>2000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>2100</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M48" s="3">
-        <v>2100</v>
-      </c>
-      <c r="N48" s="3">
-        <v>2200</v>
       </c>
       <c r="O48" s="3">
         <v>2200</v>
@@ -3502,25 +3610,25 @@
         <v>2200</v>
       </c>
       <c r="Q48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="R48" s="3">
         <v>2300</v>
-      </c>
-      <c r="R48" s="3">
-        <v>300</v>
       </c>
       <c r="S48" s="3">
         <v>300</v>
       </c>
       <c r="T48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U48" s="3">
         <v>400</v>
       </c>
       <c r="V48" s="3">
+        <v>400</v>
+      </c>
+      <c r="W48" s="3">
         <v>500</v>
-      </c>
-      <c r="W48" s="3">
-        <v>600</v>
       </c>
       <c r="X48" s="3">
         <v>600</v>
@@ -3529,90 +3637,96 @@
         <v>600</v>
       </c>
       <c r="Z48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AA48" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>500</v>
-      </c>
-      <c r="E49" s="3">
-        <v>600</v>
-      </c>
-      <c r="F49" s="3">
-        <v>600</v>
-      </c>
-      <c r="G49" s="3">
-        <v>700</v>
-      </c>
-      <c r="H49" s="3">
-        <v>900</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" s="3">
         <v>1100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2200</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>2600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2800</v>
-      </c>
-      <c r="O49" s="3">
-        <v>3000</v>
       </c>
       <c r="P49" s="3">
         <v>3000</v>
       </c>
       <c r="Q49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R49" s="3">
         <v>2900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3700</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>3900</v>
       </c>
       <c r="Z49" s="3">
         <v>3900</v>
       </c>
       <c r="AA49" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AB49" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,8 +3882,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3797,14 +3917,14 @@
       <c r="L52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N52" s="3">
         <v>4500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4700</v>
-      </c>
-      <c r="O52" s="3">
-        <v>4800</v>
       </c>
       <c r="P52" s="3">
         <v>4800</v>
@@ -3813,19 +3933,19 @@
         <v>4800</v>
       </c>
       <c r="R52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="S52" s="3">
         <v>5200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5700</v>
-      </c>
-      <c r="V52" s="3">
-        <v>5200</v>
       </c>
       <c r="W52" s="3">
         <v>5200</v>
@@ -3837,13 +3957,16 @@
         <v>5200</v>
       </c>
       <c r="Z52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AA52" s="3">
         <v>5300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>13000</v>
-      </c>
-      <c r="E54" s="3">
-        <v>19200</v>
-      </c>
-      <c r="F54" s="3">
-        <v>19200</v>
-      </c>
-      <c r="G54" s="3">
-        <v>18500</v>
-      </c>
-      <c r="H54" s="3">
-        <v>17600</v>
-      </c>
-      <c r="I54" s="3">
-        <v>25600</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K54" s="3">
         <v>25100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21800</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N54" s="3">
         <v>21100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>22400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>21300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>21700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>20700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>20000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>19100</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>19200</v>
       </c>
       <c r="Z54" s="3">
         <v>19200</v>
       </c>
       <c r="AA54" s="3">
+        <v>19200</v>
+      </c>
+      <c r="AB54" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,76 +4184,77 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>100</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G57" s="3">
-        <v>100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K57" s="3">
+        <v>200</v>
+      </c>
+      <c r="L57" s="3">
+        <v>400</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N57" s="3">
+        <v>400</v>
+      </c>
+      <c r="O57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
-        <v>200</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="P57" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q57" s="3">
         <v>400</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M57" s="3">
-        <v>400</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1100</v>
-      </c>
-      <c r="O57" s="3">
-        <v>500</v>
-      </c>
-      <c r="P57" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>200</v>
       </c>
       <c r="R57" s="3">
         <v>200</v>
       </c>
       <c r="S57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T57" s="3">
         <v>300</v>
       </c>
       <c r="U57" s="3">
+        <v>300</v>
+      </c>
+      <c r="V57" s="3">
         <v>500</v>
-      </c>
-      <c r="V57" s="3">
-        <v>300</v>
       </c>
       <c r="W57" s="3">
         <v>300</v>
       </c>
       <c r="X57" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y57" s="3">
         <v>600</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>400</v>
       </c>
       <c r="Z57" s="3">
         <v>400</v>
@@ -4131,40 +4262,43 @@
       <c r="AA57" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>100</v>
-      </c>
-      <c r="E58" s="3">
-        <v>100</v>
-      </c>
-      <c r="F58" s="3">
-        <v>100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>100</v>
-      </c>
-      <c r="H58" s="3">
-        <v>100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>100</v>
-      </c>
-      <c r="J58" s="3">
-        <v>100</v>
+      <c r="D58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>100</v>
@@ -4179,7 +4313,7 @@
         <v>100</v>
       </c>
       <c r="R58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -4188,17 +4322,17 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>400</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>17</v>
       </c>
@@ -4208,40 +4342,43 @@
       <c r="AA58" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>300</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
-        <v>500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>500</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M59" s="3">
-        <v>400</v>
+      <c r="M59" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N59" s="3">
         <v>400</v>
@@ -4250,152 +4387,158 @@
         <v>400</v>
       </c>
       <c r="P59" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q59" s="3">
         <v>500</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>600</v>
       </c>
       <c r="R59" s="3">
         <v>600</v>
       </c>
       <c r="S59" s="3">
+        <v>600</v>
+      </c>
+      <c r="T59" s="3">
         <v>700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>500</v>
-      </c>
-      <c r="E60" s="3">
-        <v>500</v>
-      </c>
-      <c r="F60" s="3">
-        <v>500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>500</v>
-      </c>
-      <c r="H60" s="3">
-        <v>500</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N60" s="3">
+        <v>900</v>
+      </c>
+      <c r="O60" s="3">
         <v>1500</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K60" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M60" s="3">
-        <v>900</v>
-      </c>
-      <c r="N60" s="3">
-        <v>1500</v>
-      </c>
-      <c r="O60" s="3">
-        <v>1000</v>
       </c>
       <c r="P60" s="3">
         <v>1000</v>
       </c>
       <c r="Q60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R60" s="3">
         <v>900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>800</v>
-      </c>
-      <c r="U60" s="3">
-        <v>1500</v>
       </c>
       <c r="V60" s="3">
         <v>1500</v>
       </c>
       <c r="W60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X60" s="3">
         <v>1400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>1600</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="M61" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>1600</v>
@@ -4404,13 +4547,13 @@
         <v>1600</v>
       </c>
       <c r="P61" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="Q61" s="3">
         <v>1700</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -4419,17 +4562,17 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>500</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4439,8 +4582,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4471,8 +4617,8 @@
       <c r="L62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -4514,10 +4660,13 @@
         <v>0</v>
       </c>
       <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K66" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O66" s="3">
+        <v>3200</v>
+      </c>
+      <c r="P66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="R66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="S66" s="3">
+        <v>700</v>
+      </c>
+      <c r="T66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U66" s="3">
+        <v>800</v>
+      </c>
+      <c r="V66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="W66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="X66" s="3">
         <v>2000</v>
-      </c>
-      <c r="E66" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F66" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>3100</v>
-      </c>
-      <c r="J66" s="3">
-        <v>3000</v>
-      </c>
-      <c r="K66" s="3">
-        <v>2600</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M66" s="3">
-        <v>2500</v>
-      </c>
-      <c r="N66" s="3">
-        <v>3200</v>
-      </c>
-      <c r="O66" s="3">
-        <v>2600</v>
-      </c>
-      <c r="P66" s="3">
-        <v>2700</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>2600</v>
-      </c>
-      <c r="R66" s="3">
-        <v>700</v>
-      </c>
-      <c r="S66" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T66" s="3">
-        <v>800</v>
-      </c>
-      <c r="U66" s="3">
-        <v>2100</v>
-      </c>
-      <c r="V66" s="3">
-        <v>1900</v>
-      </c>
-      <c r="W66" s="3">
-        <v>2000</v>
-      </c>
-      <c r="X66" s="3">
-        <v>1300</v>
       </c>
       <c r="Y66" s="3">
         <v>1300</v>
       </c>
       <c r="Z66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA66" s="3">
         <v>1400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,8 +5332,11 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5196,50 +5370,53 @@
       <c r="M72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N72" s="3">
-        <v>-6300</v>
+      <c r="N72" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="O72" s="3">
         <v>-6300</v>
       </c>
       <c r="P72" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5100</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-4300</v>
       </c>
       <c r="S72" s="3">
         <v>-4300</v>
       </c>
       <c r="T72" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="U72" s="3">
         <v>-4400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>11000</v>
-      </c>
-      <c r="E76" s="3">
-        <v>17100</v>
-      </c>
-      <c r="F76" s="3">
-        <v>17200</v>
-      </c>
-      <c r="G76" s="3">
-        <v>16400</v>
-      </c>
-      <c r="H76" s="3">
-        <v>15600</v>
-      </c>
-      <c r="I76" s="3">
-        <v>22500</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K76" s="3">
         <v>22100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N76" s="3">
         <v>18600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>20700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>18000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M81" s="3">
+        <v>800</v>
+      </c>
+      <c r="N81" s="3">
+        <v>500</v>
+      </c>
+      <c r="O81" s="3">
+        <v>600</v>
+      </c>
+      <c r="P81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S81" s="3">
+        <v>600</v>
+      </c>
+      <c r="T81" s="3">
+        <v>800</v>
+      </c>
+      <c r="U81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V81" s="3">
         <v>400</v>
       </c>
-      <c r="E81" s="3">
-        <v>800</v>
-      </c>
-      <c r="F81" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>900</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J81" s="3">
-        <v>3500</v>
-      </c>
-      <c r="K81" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L81" s="3">
-        <v>800</v>
-      </c>
-      <c r="M81" s="3">
-        <v>500</v>
-      </c>
-      <c r="N81" s="3">
-        <v>600</v>
-      </c>
-      <c r="O81" s="3">
-        <v>100</v>
-      </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R81" s="3">
-        <v>600</v>
-      </c>
-      <c r="S81" s="3">
-        <v>800</v>
-      </c>
-      <c r="T81" s="3">
-        <v>1100</v>
-      </c>
-      <c r="U81" s="3">
-        <v>400</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>200</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-100</v>
       </c>
       <c r="Y81" s="3">
         <v>-100</v>
       </c>
       <c r="Z81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA81" s="3">
         <v>6100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,16 +6009,17 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>200</v>
-      </c>
-      <c r="E83" s="3">
-        <v>200</v>
+      <c r="D83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>17</v>
@@ -5828,14 +6027,14 @@
       <c r="G83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H83" s="3">
-        <v>200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="H83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5844,16 +6043,16 @@
         <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
       </c>
       <c r="O83" s="3">
+        <v>200</v>
+      </c>
+      <c r="P83" s="3">
         <v>500</v>
-      </c>
-      <c r="P83" s="3">
-        <v>200</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
@@ -5874,10 +6073,10 @@
         <v>200</v>
       </c>
       <c r="W83" s="3">
+        <v>200</v>
+      </c>
+      <c r="X83" s="3">
         <v>300</v>
-      </c>
-      <c r="X83" s="3">
-        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N89" s="3">
+        <v>400</v>
+      </c>
+      <c r="O89" s="3">
+        <v>200</v>
+      </c>
+      <c r="P89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S89" s="3">
+        <v>800</v>
+      </c>
+      <c r="T89" s="3">
+        <v>900</v>
+      </c>
+      <c r="U89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V89" s="3">
         <v>1000</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F89" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G89" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L89" s="3">
-        <v>1100</v>
-      </c>
-      <c r="M89" s="3">
-        <v>400</v>
-      </c>
-      <c r="N89" s="3">
-        <v>200</v>
-      </c>
-      <c r="O89" s="3">
-        <v>100</v>
-      </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>1100</v>
-      </c>
-      <c r="R89" s="3">
-        <v>800</v>
-      </c>
-      <c r="S89" s="3">
-        <v>900</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="U89" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>600</v>
-      </c>
-      <c r="W89" s="3">
-        <v>500</v>
       </c>
       <c r="X89" s="3">
         <v>500</v>
       </c>
       <c r="Y89" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z89" s="3">
         <v>400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,85 +6599,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,64 +6837,67 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M94" s="3">
+        <v>100</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="O94" s="3">
         <v>1900</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F94" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H94" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>6900</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L94" s="3">
-        <v>100</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="N94" s="3">
-        <v>1900</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2400</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T94" s="3">
         <v>-100</v>
       </c>
       <c r="U94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -6676,19 +6906,22 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y94" s="3">
         <v>-100</v>
       </c>
       <c r="Z94" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="AA94" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,28 +6949,29 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>6600</v>
+      <c r="D96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F96" s="3">
-        <v>700</v>
-      </c>
-      <c r="G96" s="3">
-        <v>700</v>
-      </c>
-      <c r="H96" s="3">
-        <v>7900</v>
-      </c>
-      <c r="I96" s="3">
-        <v>1400</v>
+      <c r="F96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>17</v>
@@ -6748,17 +6982,17 @@
       <c r="L96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N96" s="3">
         <v>-600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1300</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-600</v>
       </c>
       <c r="Q96" s="3">
         <v>-600</v>
@@ -6767,7 +7001,7 @@
         <v>-600</v>
       </c>
       <c r="S96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="T96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,28 +7267,31 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-6600</v>
+      <c r="D100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F100" s="3">
-        <v>-700</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-1400</v>
+      <c r="F100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>17</v>
@@ -7053,32 +7299,32 @@
       <c r="K100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M100" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="N100" s="3">
         <v>-700</v>
       </c>
       <c r="O100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P100" s="3">
         <v>-1300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1100</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-600</v>
       </c>
       <c r="S100" s="3">
         <v>-600</v>
       </c>
       <c r="T100" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -7087,11 +7333,11 @@
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>900</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
@@ -7101,16 +7347,19 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>17</v>
@@ -7118,141 +7367,147 @@
       <c r="G101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="H101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L101" s="3">
         <v>-100</v>
       </c>
       <c r="M101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-100</v>
-      </c>
-      <c r="U101" s="3">
-        <v>100</v>
       </c>
       <c r="V101" s="3">
         <v>100</v>
       </c>
       <c r="W101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-3700</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N102" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="O102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P102" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="R102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S102" s="3">
+        <v>100</v>
+      </c>
+      <c r="T102" s="3">
+        <v>200</v>
+      </c>
+      <c r="U102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V102" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W102" s="3">
+        <v>600</v>
+      </c>
+      <c r="X102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="I102" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
-        <v>1100</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="N102" s="3">
-        <v>1500</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="P102" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="R102" s="3">
-        <v>100</v>
-      </c>
-      <c r="S102" s="3">
-        <v>200</v>
-      </c>
-      <c r="T102" s="3">
-        <v>-400</v>
-      </c>
-      <c r="U102" s="3">
-        <v>1100</v>
-      </c>
-      <c r="V102" s="3">
-        <v>600</v>
-      </c>
-      <c r="W102" s="3">
-        <v>1400</v>
-      </c>
-      <c r="X102" s="3">
-        <v>300</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>300</v>
       </c>
     </row>
